--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,13 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,14 +772,14 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>19.9</v>
+      <c r="D4" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n">
@@ -806,20 +794,20 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="12" t="n">
-        <v>16</v>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>451.2</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0.1</v>
@@ -831,7 +819,7 @@
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -843,13 +831,13 @@
         <v>11</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -868,8 +856,8 @@
       <c r="D5" s="9" t="n">
         <v>26.51</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>14</v>
+      <c r="E5" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>20.3</v>
@@ -878,7 +866,7 @@
         <v>42.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>20.5</v>
@@ -892,15 +880,15 @@
       <c r="L5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>13.9</v>
+      <c r="M5" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>1.4</v>
@@ -909,28 +897,28 @@
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>90.5</v>
+        <v>0.5</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.2</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -948,14 +936,14 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>14.3</v>
+      <c r="D6" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19.3</v>
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.1</v>
@@ -967,38 +955,38 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>26.1</v>
+        <v>5.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R6" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1007,13 +995,13 @@
         <v>2.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1029,29 +1017,29 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>41.2</v>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>24.4</v>
@@ -1059,44 +1047,44 @@
       <c r="M7" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="N7" s="12" t="n">
-        <v>67.09999999999999</v>
+      <c r="N7" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.2</v>
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X7" s="12" t="n">
-        <v>81.3</v>
+        <v>7</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,16 +1100,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>327.9</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>19.9</v>
+      <c r="E8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>9.6</v>
@@ -1131,7 +1119,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1139,18 +1127,18 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="12" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>318.9</v>
+      <c r="M8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>29.8</v>
       </c>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1159,10 +1147,10 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>7.2</v>
+        <v>72</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.8</v>
@@ -1171,13 +1159,13 @@
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.2</v>
+        <v>10.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1191,7 @@
         <v>19.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1212,18 +1200,18 @@
         <v>61.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1128.9</v>
+        <v>8.9</v>
       </c>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n">
-        <v>108.2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
@@ -1233,23 +1221,23 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>393.1</v>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n">
-        <v>95.5</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>87.2</v>
+        <v>80.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>94.8</v>
+        <v>994.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>429</v>
+        <v>929</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>1.6</v>
@@ -1273,11 +1261,11 @@
       <c r="D10" s="10" t="n">
         <v>165.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>14.3</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>9.9</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>55</v>
@@ -1286,21 +1274,23 @@
         <v>61.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>74.3</v>
+        <v>29.3</v>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n">
-        <v>118.6</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.8</v>
@@ -1315,25 +1305,25 @@
         <v>44.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>91.40000000000001</v>
+      <c r="V10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="X10" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1351,22 +1341,22 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>197.5</v>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
@@ -1378,16 +1368,16 @@
         <v>98.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="R11" s="12" t="n">
-        <v>81.7</v>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>89.5</v>
+        <v>9.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1.2</v>
@@ -1395,14 +1385,14 @@
       <c r="U11" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V11" s="12" t="n">
-        <v>18.6</v>
+      <c r="V11" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>20.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>1.1</v>
@@ -1422,20 +1412,20 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E12" s="13" t="n"/>
+        <v>23.9</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>41.8</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>10</v>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
@@ -1445,32 +1435,32 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="12" t="n">
-        <v>78.90000000000001</v>
+      <c r="M12" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>14.9</v>
+        <v>0.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>858.9</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.2</v>
@@ -1479,13 +1469,13 @@
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>93.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1501,16 +1491,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>51.7</v>
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.7</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>19.8</v>
+      <c r="F13" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>13</v>
@@ -1519,34 +1509,34 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
@@ -1564,10 +1554,10 @@
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1584,14 +1574,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
-        <v>24.6</v>
+      <c r="D14" s="9" t="n">
+        <v>54.6</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <v>2.3</v>
+      <c r="F14" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>114.4</v>
@@ -1606,7 +1596,7 @@
         <v>2.8</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>12.5</v>
@@ -1615,11 +1605,11 @@
         <v>1.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>24.6</v>
@@ -1633,23 +1623,23 @@
       <c r="T14" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>20.6</v>
+      <c r="U14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1668,14 +1658,14 @@
       <c r="D15" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>19.1</v>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.1</v>
@@ -1684,10 +1674,10 @@
         <v>2.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>4.4</v>
@@ -1697,11 +1687,11 @@
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1710,10 +1700,10 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
@@ -1721,11 +1711,11 @@
       <c r="W15" s="3" t="n">
         <v>83.5</v>
       </c>
-      <c r="X15" s="12" t="n">
-        <v>88.59999999999999</v>
+      <c r="X15" s="8" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1748,37 +1738,37 @@
         <v>26.7</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>14.9</v>
+        <v>9</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>23.6</v>
+        <v>2.6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>481.9</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>4.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>97.8</v>
+        <v>90</v>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
@@ -1788,10 +1778,10 @@
         <v>1.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
@@ -1800,10 +1790,10 @@
         <v>4094.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>41.1</v>
@@ -1829,10 +1819,10 @@
         <v>172.1</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>65.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>19.1</v>
+        <v>0.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>62</v>
@@ -1844,25 +1834,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>66.2</v>
+        <v>60</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
@@ -1871,28 +1864,28 @@
         <v>46.1</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="U17" s="12" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>20.1</v>
+        <v>2.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>190.9</v>
+        <v>1.8</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>100.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>81.7</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1908,23 +1901,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>9.800000000000001</v>
+      <c r="E18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.7</v>
@@ -1934,13 +1927,13 @@
       </c>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>998.6</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0</v>
@@ -1948,26 +1941,26 @@
       <c r="Q18" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="R18" s="12" t="n">
-        <v>19</v>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>742</v>
+        <v>10</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>15.1</v>
+        <v>10</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>63.2</v>
@@ -1992,11 +1985,11 @@
       <c r="D19" s="9" t="n">
         <v>142.51</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>19.9</v>
+      <c r="E19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>9.6</v>
@@ -2005,11 +1998,11 @@
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n"/>
-      <c r="M19" s="12" t="n">
-        <v>14.9</v>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
@@ -2023,10 +2016,10 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
@@ -2038,10 +2031,10 @@
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2063,23 +2056,23 @@
       <c r="D20" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>10.6</v>
+      <c r="E20" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
@@ -2088,16 +2081,16 @@
         <v>0.3</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>96.8</v>
+        <v>6</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>231.4</v>
@@ -2105,17 +2098,17 @@
       <c r="R20" s="3" t="n">
         <v>115.1</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>91.2</v>
+        <v>2</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>42.2</v>
@@ -2124,10 +2117,10 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2146,14 +2139,14 @@
       <c r="D21" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>19.8</v>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n">
@@ -2163,52 +2156,52 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
+        <v>10</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2227,23 +2220,23 @@
       <c r="D22" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>90.59999999999999</v>
+      <c r="E22" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>5.1</v>
@@ -2252,44 +2245,44 @@
         <v>16.5</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>16.3</v>
+        <v>0.3</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1188.8</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>99.8</v>
+        <v>29</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>12.7</v>
+        <v>1.3</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>161.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2310,17 +2303,17 @@
       <c r="D23" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>66.8</v>
+      <c r="E23" s="10" t="n">
+        <v>50.8</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>12.7</v>
+        <v>10.7</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>61.4</v>
+        <v>1.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53.9</v>
+        <v>53</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>2.5</v>
@@ -2329,45 +2322,45 @@
         <v>3.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>43.2</v>
       </c>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>115.6</v>
+        <v>53.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
+        <v>1.5</v>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n">
         <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>219.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.3</v>
+        <v>9.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>86.3</v>
+        <v>80</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>76.7</v>
@@ -2390,40 +2383,40 @@
         <v>25.6</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="12" t="n">
-        <v>1.7</v>
+      <c r="L24" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R24" s="12" t="n">
-        <v>18.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.9</v>
@@ -2434,20 +2427,20 @@
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="V24" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X24" s="12" t="n">
-        <v>17.8</v>
+        <v>0</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2467,7 +2460,7 @@
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.3</v>
@@ -2479,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>22</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.1</v>
@@ -2491,22 +2484,22 @@
         <v>1.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="Q25" s="12" t="n">
-        <v>1156.1</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>1.2</v>
@@ -2515,16 +2508,18 @@
         <v>0.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X25" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="3" t="n">
         <v>95</v>
       </c>
@@ -2545,22 +2540,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>22.8</v>
+        <v>1.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>19.3</v>
+        <v>13.5</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n">
@@ -2576,38 +2571,38 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W26" s="12" t="n">
-        <v>15.3</v>
+        <v>10.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2635,10 +2630,10 @@
       </c>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>4.3</v>
@@ -2648,16 +2643,16 @@
         <v>15.8</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>12.8</v>
+        <v>20</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>18</v>
@@ -2666,13 +2661,13 @@
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>19</v>
@@ -2681,13 +2676,13 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>21.8</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2706,8 +2701,8 @@
       <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>13.3</v>
+      <c r="E28" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>18.9</v>
@@ -2726,32 +2721,32 @@
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="12" t="n">
-        <v>19.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2760,10 +2755,10 @@
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>99.8</v>
+        <v>10</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.9</v>
@@ -2788,15 +2783,15 @@
       <c r="E29" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>81.7</v>
+      <c r="F29" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.6</v>
@@ -2811,40 +2806,40 @@
         <v>44.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>434.3</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>19</v>
+      <c r="R29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W29" s="12" t="n">
-        <v>31</v>
+        <v>0.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.2</v>
+        <v>9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2863,20 +2858,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1116.8</v>
-      </c>
-      <c r="D30" s="14" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.8</v>
@@ -2886,40 +2883,40 @@
       </c>
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>199.8</v>
+        <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4213.8</v>
+        <v>1.3</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>21.8</v>
+        <v>1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>1.3</v>
@@ -2944,9 +2941,11 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="D31" s="3" t="n"/>
+        <v>23.9</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="10" t="n">
         <v>71.90000000000001</v>
       </c>
@@ -2954,10 +2953,10 @@
         <v>14.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>3.9</v>
@@ -2966,48 +2965,48 @@
         <v>2.5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>74.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>7058</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W31" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="W31" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3023,31 +3022,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144 1
-</t>
-        </is>
+      <c r="E32" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
@@ -3057,47 +3053,44 @@
         <v>14.9</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.2</v>
+        <v>12</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>180.9</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R32" s="12" t="n">
+      <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="V32" s="3" t="n"/>
-      <c r="W32" s="12" t="n">
-        <v>16.2</v>
+      <c r="W32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">0 0 0
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 13
-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3113,7 +3106,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>90.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>22.8</v>
@@ -3124,11 +3117,11 @@
       <c r="F33" s="9" t="n">
         <v>81.33</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.3</v>
+      <c r="G33" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
@@ -3138,32 +3131,32 @@
         <v>39.1</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
@@ -3172,13 +3165,13 @@
         <v>6.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>89.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3194,17 +3187,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="12" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>13.7</v>
+      <c r="D34" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3.7</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>81.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.4</v>
@@ -3214,36 +3207,36 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>14.2</v>
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n"/>
       <c r="P34" s="3" t="n">
-        <v>10.6</v>
+        <v>20</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n">
-        <v>17.3</v>
+        <v>10</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96.8</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>16.4</v>
+        <v>0.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>52.2</v>
@@ -3255,7 +3248,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3274,69 +3267,69 @@
       <c r="D35" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>14.2</v>
+      <c r="E35" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>15.1</v>
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>76.90000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>15.9</v>
+        <v>10</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="W35" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X35" s="12" t="n">
-        <v>86.59999999999999</v>
+      <c r="W35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>218.6</v>
+        <v>0.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3358,11 +3351,11 @@
       <c r="E36" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -3374,23 +3367,23 @@
         <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="12" t="n">
-        <v>66.40000000000001</v>
+      <c r="N36" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>28.9</v>
+        <v>3</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>1.4</v>
@@ -3399,10 +3392,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>10</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3411,13 +3404,13 @@
         <v>2.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3434,44 +3427,49 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>13.8</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>19.5</v>
+        <v>0.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 0
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.1</v>
+        <v>0.7</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>987.8</v>
+        <v>20</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>89.90000000000001</v>
@@ -3487,7 +3485,7 @@
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>7.6</v>
@@ -3496,7 +3494,7 @@
         <v>42.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3515,50 +3513,50 @@
       <c r="D38" s="10" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
+      <c r="E38" s="12" t="n"/>
       <c r="F38" s="10" t="n">
-        <v>92.2</v>
+        <v>2.2</v>
       </c>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n">
-        <v>56.9</v>
+        <v>50.9</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>81.3</v>
+      <c r="L38" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>90</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q38" s="12" t="n">
-        <v>18</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>90</v>
@@ -3570,10 +3568,10 @@
         <v>126.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>185.9</v>
+        <v>5.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3591,72 +3589,72 @@
       <c r="C39" s="3" t="n">
         <v>44.3</v>
       </c>
-      <c r="D39" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>13.2</v>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>13.7</v>
+      <c r="L39" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>15.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P39" s="12" t="n">
-        <v>8.4</v>
+        <v>9</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="12" t="n">
-        <v>81</v>
+      <c r="V39" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3672,74 +3670,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
+        <v>6.3</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>85.09999999999999</v>
+      <c r="E40" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16.3</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>17.6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>41.3</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>92.2</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="n">
-        <v>24.8</v>
+        <v>29.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>85.8</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>62.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>116.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3755,19 +3753,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>15.97</v>
+      <c r="E41" s="8" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>16.2</v>
+        <v>17</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>34.7</v>
@@ -3782,31 +3780,31 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>1.3</v>
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
@@ -3818,13 +3816,13 @@
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39.8</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3840,23 +3838,23 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E42" s="13" t="n"/>
+        <v>60.9</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.1</v>
@@ -3865,34 +3863,34 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>12.3</v>
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>920</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25.2</v>
+        <v>20</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>49.8</v>
+        <v>99</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -3904,10 +3902,10 @@
         <v>0.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3923,79 +3921,82 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>12.4</v>
+        <v>5</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2.9</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>0.5</v>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I43" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>90</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S43" s="12" t="n">
-        <v>61.8</v>
+      <c r="S43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>18.9</v>
+        <v>10</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>20.5</v>
+        <v>5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4011,76 +4012,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.1</v>
+        <v>3109.5</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>0.5</v>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I44" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>5002</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>10110110.1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S44" s="12" t="n">
-        <v>11</v>
+        <v>20.8</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>150115100011.5</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V44" s="12" t="n">
-        <v>1989.8</v>
+        <v>0</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>2.2</v>
@@ -4099,7 +4103,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
+        <v>3109.5</v>
       </c>
       <c r="D45" s="10" t="n">
         <v>31.3</v>
@@ -4108,34 +4112,34 @@
         <v>53.4</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>92.5</v>
+        <v>22.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>56.9</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>53.1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>621.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>498</v>
+        <v>90</v>
       </c>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
@@ -4145,25 +4149,25 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2929.8</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>729.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>108.9</v>
+        <v>1208.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>328.8</v>
+        <v>300.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>2.2</v>
@@ -4185,7 +4189,7 @@
         <v>223.9</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>26.2</v>
+        <v>20.2</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>23.1</v>
@@ -4208,47 +4212,47 @@
       <c r="K46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>11.1</v>
+      <c r="L46" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>13.1</v>
+        <v>0.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <v>4.4</v>
+        <v>9</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.3</v>
+        <v>1.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>8.9</v>
+        <v>50</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>208.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,10 +152,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +168,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -771,73 +783,73 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
+        <v>289.1</v>
+      </c>
       <c r="D4" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>3.8</v>
+        <v>25.9</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>113.8</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>1</v>
+      <c r="I4" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
+        <v>27.8</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>451.2</v>
+        <v>13.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>266.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3.3</v>
+        <v>21.1</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>11</v>
+        <v>43.2</v>
+      </c>
+      <c r="W4" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>10.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -852,73 +864,75 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>1564.3</v>
+      </c>
       <c r="D5" s="9" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>20.3</v>
+        <v>25.5</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>3.5</v>
+      <c r="H5" s="10" t="n">
+        <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="L5" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R5" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5</v>
+        <v>20.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>94.8</v>
+        <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>17.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="W5" s="10" t="n">
+        <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>10</v>
+        <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -936,72 +950,72 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>9.9</v>
+      <c r="D6" s="9" t="n">
+        <v>24.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>9</v>
+        <v>4.3</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>19.3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
+      <c r="H6" s="10" t="n">
+        <v>1141.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>22</v>
+      <c r="M6" s="10" t="n">
+        <v>994.2</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>10.1</v>
+        <v>44.4</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62</v>
+        <v>671.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1</v>
+        <v>1103.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1017,74 +1031,70 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255</v>
+        <v>355.7</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F7" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>10.7</v>
+      <c r="G7" s="10" t="n">
+        <v>80.09999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>24.4</v>
+        <v>41.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>4.2</v>
+        <v>52.2</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>298.5</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>41.1</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>18.8</v>
+        <v>12.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1100,72 +1110,72 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>4.8</v>
+      <c r="E8" s="10" t="n">
+        <v>14.8</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+        <v>19.6</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>441.2</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>31</v>
+        <v>5.2</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>4971.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="P8" s="3" t="n"/>
+        <v>99.8</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R8" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="V8" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>17.8</v>
+      <c r="W8" s="10" t="n">
+        <v>917.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>10.2</v>
+        <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1180,40 +1190,42 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>19.6</v>
+      <c r="C9" s="3" t="n">
+        <v>182528.1</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="9" t="n">
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.5</v>
+        <v>161.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>61.6</v>
+        <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
+        <v>21.7</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>28.9</v>
+      </c>
       <c r="L9" s="3" t="n">
-        <v>4.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N9" s="3" t="n"/>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="n">
         <v>103.3</v>
       </c>
@@ -1221,26 +1233,26 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.6</v>
+        <v>195.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>393.1</v>
-      </c>
-      <c r="U9" s="3" t="n"/>
+        <v>998.8</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="n">
-        <v>0</v>
+        <v>295.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.2</v>
+        <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>994.8</v>
+        <v>194.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>929</v>
+        <v>19429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1256,45 +1268,39 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>156.3</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>165.1</v>
-      </c>
-      <c r="E10" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>61.5</v>
-      </c>
+      <c r="F10" s="12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="M10" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -1302,28 +1308,22 @@
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>44.1</v>
+        <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X10" s="8" t="n">
-        <v>10</v>
+        <v>19.1</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9</v>
+        <v>38.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1339,65 +1339,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="3" t="n">
+        <v>329.6</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N11" s="3" t="n"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="10" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>9.5</v>
+        <v>92.8</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>811.4</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>289.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.2</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>20.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>98.8</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1412,70 +1416,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="9" t="n">
-        <v>0</v>
+        <v>521.2</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>4.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>41.8</v>
+        <v>41.3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>22.2</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>12</v>
+      <c r="M12" s="10" t="n">
+        <v>24.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99</v>
+        <v>299.9</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>0.9</v>
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>46.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>188.6</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V12" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="V12" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1491,58 +1501,58 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>9455.6</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F13" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>4.4</v>
+        <v>41.1</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>717.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>20.8</v>
+        <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>166.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1551,15 +1561,17 @@
         <v>20.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="Z13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1573,46 +1585,50 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>23</v>
+      <c r="C14" s="3" t="n">
+        <v>20319.9</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>19.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>114.4</v>
+        <v>441.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="I14" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.7</v>
-      </c>
       <c r="L14" s="3" t="n">
-        <v>12.5</v>
+        <v>43.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>820.2</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>929</v>
+      </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>18.8</v>
@@ -1620,26 +1636,22 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="10" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W14" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1654,44 +1666,44 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>484.5</v>
+      </c>
       <c r="D15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0</v>
+        <v>26.7</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="G15" s="10" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P15" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23</v>
+        <v>2.1</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1700,25 +1712,21 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>948</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>80.59999999999999</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>89</v>
+        <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.6</v>
+        <v>31.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1733,73 +1741,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>95.7</v>
+      <c r="C16" s="3" t="n">
+        <v>2326.9</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>295.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.6</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>195481.9</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>3</v>
+        <v>113.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0</v>
+        <v>166.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>4.1</v>
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>19491</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Q16" s="3" t="n">
         <v>115.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
+        <v>5.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>4094.8</v>
+        <v>10</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20</v>
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>41.1</v>
+        <v>929</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1814,78 +1824,73 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="10" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>62</v>
+      <c r="C17" s="3" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>824.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="M17" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="S17" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S17" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>0</v>
+        <v>562.6</v>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="10" t="n">
+        <v>1.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>100.9</v>
+        <v>18.2</v>
+      </c>
+      <c r="X17" s="10" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>898</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8</v>
+        <v>297.4</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1900,73 +1905,67 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0</v>
+      <c r="C18" s="3" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>2.7</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.3</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R18" s="10" t="n">
+        <v>719</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="V18" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="W18" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>10</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>63.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1981,31 +1980,39 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="9" t="n">
-        <v>142.51</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>9.699999999999999</v>
+      <c r="C19" s="3" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>116.26</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>196.8</v>
+      </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
@@ -2016,25 +2023,23 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>894.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2052,75 +2057,67 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.6</v>
+      <c r="C20" s="3" t="n">
+        <v>494.9</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="13" t="n">
+        <v>124.94</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.3</v>
+        <v>12.6</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>231.4</v>
+        <v>221.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="S20" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S20" s="10" t="n">
         <v>16.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>28</v>
-      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0.2</v>
+        <v>19.2</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="Y20" s="3" t="n">
-        <v>80</v>
-      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
       <c r="Z20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2135,74 +2132,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>379.3</v>
+      </c>
       <c r="D21" s="3" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n">
-        <v>0.3</v>
+        <v>25.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>88.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>12.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N21" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
+        <v>19.3</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>16.5</v>
+        <v>94.7</v>
+      </c>
+      <c r="V21" s="10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W21" s="10" t="n">
+        <v>169.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>18.6</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2216,74 +2209,70 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F22" s="9" t="n">
+      <c r="C22" s="3" t="n">
+        <v>508.9</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P22" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R22" s="3" t="n">
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="10" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>10</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>29</v>
+        <v>9.4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V22" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20</v>
+        <v>36.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z22" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2298,72 +2287,74 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>10.7</v>
+        <v>2089.4</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>1128.5</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>4.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.9</v>
+        <v>1161.4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.5</v>
+        <v>110.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>115.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>20.5</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>22</v>
+        <v>29489</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>53.6</v>
+        <v>1113.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" s="3" t="n"/>
+        <v>14.5</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>191.8</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>2328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1219.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>9.4</v>
+        <v>194.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>80</v>
+        <v>186.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>9429</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>76.7</v>
+        <v>116.9</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2378,70 +2369,64 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="10" t="n">
+      <c r="C24" s="3" t="n">
+        <v>43791.8</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="E24" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="10" t="n">
+        <v>21565.9</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="n"/>
+        <v>4.4</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>97.8</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>39.9</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>10.8</v>
+      <c r="V24" s="10" t="n">
+        <v>189.4</v>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="10" t="n">
+        <v>8881.200000000001</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z24" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2455,76 +2440,71 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
+        <v>233.6</v>
+      </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>0</v>
+      <c r="E25" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>872.6</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>10.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0
-</t>
-        </is>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>1.2</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.9</v>
+        <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="U25" s="3" t="n"/>
+        <v>111.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2540,71 +2520,73 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.2</v>
+        <v>258.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+      <c r="I26" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M26" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="10" t="n">
         <v>15.8</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="M26" s="10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="R26" s="3" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>3</v>
+        <v>931.8</v>
       </c>
       <c r="U26" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="W26" s="10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2618,71 +2600,69 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C27" s="3" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.6</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="10" t="n">
+        <v>183.5</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>0</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>18</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>28.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="10" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X27" s="3" t="inlineStr"/>
       <c r="Y27" s="3" t="n">
-        <v>28</v>
+        <v>88.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2697,71 +2677,71 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
+        <v>331.3</v>
+      </c>
       <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
+      <c r="E28" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>18.17</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I28" s="3" t="n"/>
+      <c r="H28" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K28" s="10" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="n"/>
+        <v>44.5</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>0.8</v>
+        <v>98</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="10" t="n">
+        <v>19.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2</v>
+        <v>42.2</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>10</v>
+        <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17</v>
+        <v>41.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2776,70 +2756,68 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>309.1</v>
+      </c>
       <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="E29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="10" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>44.5</v>
+        <v>13.1</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>82.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>434.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>856.1</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V29" s="10" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="W29" s="10" t="n">
+        <v>1991</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>9</v>
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2858,71 +2836,67 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>8.5</v>
+        <v>1569.9</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>194.3</v>
       </c>
       <c r="G30" s="3" t="n">
+        <v>1544.9</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1629.4</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="n">
+        <v>444924.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>212.1</v>
+      </c>
+      <c r="Q30" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>23.6</v>
-      </c>
       <c r="R30" s="3" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1.3</v>
+        <v>9413.799999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1</v>
+        <v>244.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85</v>
+        <v>185.9</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>182.9</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>4250.1</v>
+        <v>922</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>4.4</v>
@@ -2941,72 +2915,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>14.3</v>
+        <v>314</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="H31" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3" t="n"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>7058</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>8115.4</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>4.6</v>
+      <c r="W31" s="10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3022,76 +2994,61 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M32" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>14.9</v>
-      </c>
       <c r="N32" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0 0
-</t>
-        </is>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3106,72 +3063,70 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>90.2</v>
+        <v>411.2</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>19</v>
+        <v>23.7</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>100</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="K33" s="3" t="n">
-        <v>39.1</v>
+        <v>2.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
+        <v>14.3</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>1097.2</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>20</v>
+        <v>99.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>191.2</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>0.6</v>
+        <v>16.4</v>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="10" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
+      </c>
+      <c r="X33" s="10" t="n">
+        <v>980</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>20</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3186,69 +3141,69 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>81.7</v>
+      <c r="C34" s="3" t="n">
+        <v>1144.4</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>10</v>
-      </c>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="3" t="n"/>
+        <v>18.8</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>299</v>
+      </c>
       <c r="P34" s="3" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>0.4</v>
+        <v>21</v>
+      </c>
+      <c r="V34" s="10" t="n">
+        <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
+        <v>43.2</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3263,73 +3218,75 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="9" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>1.2</v>
+      <c r="C35" s="3" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>30.9</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>21281.8</v>
+      </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18</v>
+        <v>23.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>60</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="3" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>5</v>
+        <v>48.4</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>6.5</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3344,73 +3301,73 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>613.2</v>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F36" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L36" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>3</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="10" t="n">
+        <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="S36" s="10" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V36" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>12.6</v>
+        <v>41.2</v>
+      </c>
+      <c r="X36" s="10" t="n">
+        <v>32.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3425,76 +3382,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>0.5</v>
+      <c r="C37" s="3" t="n">
+        <v>19782.4</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>1092.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0
-</t>
-        </is>
+        <v>32.8</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>56.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.7</v>
+        <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>150.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>10</v>
+        <v>1681.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.6</v>
+        <v>167.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20</v>
+        <v>9492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>9</v>
+        <v>401.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3819.1</v>
+        <v>382191.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V37" s="3" t="n"/>
+        <v>233.2</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="W37" s="3" t="n">
-        <v>1</v>
+        <v>181.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7.6</v>
+        <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3509,69 +3467,69 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="10" t="n">
-        <v>484.1</v>
-      </c>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="C38" s="3" t="n">
+        <v>495.6</v>
+      </c>
+      <c r="D38" s="11" t="inlineStr"/>
+      <c r="E38" s="12" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R38" s="3" t="n"/>
-      <c r="S38" s="3" t="n">
-        <v>12.6</v>
+        <v>30.2</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S38" s="10" t="n">
+        <v>172</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
-      <c r="U38" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U38" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="V38" s="10" t="n">
+        <v>8101.4</v>
+      </c>
+      <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="n">
-        <v>126.1</v>
+        <v>17.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>5.9</v>
+        <v>184.6</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3587,74 +3545,68 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44.3</v>
+        <v>624.3</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.9</v>
+        <v>25.9</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>18.15</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I39" s="3" t="n"/>
+        <v>17.6</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>8</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="10" t="n">
+        <v>2120.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q39" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.5</v>
+        <v>18.9</v>
+      </c>
+      <c r="S39" s="10" t="n">
+        <v>50.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>16</v>
+        <v>12.8</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="10" t="n">
+        <v>98.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>67</v>
+        <v>162.8</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3670,74 +3622,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>1.1</v>
+        <v>637.7</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>12.7</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>41.3</v>
+        <v>10</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>2</v>
+        <v>19.8</v>
+      </c>
+      <c r="N40" s="10" t="n">
+        <v>21.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n">
-        <v>29.8</v>
+        <v>98</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q40" s="10" t="n">
+        <v>35.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
+      </c>
+      <c r="V40" s="10" t="n">
+        <v>22.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>6.9</v>
+        <v>3.1</v>
+      </c>
+      <c r="X40" s="10" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.8</v>
+        <v>59</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0.8</v>
+        <v>26.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3753,76 +3705,66 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>794.3</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="3" t="inlineStr"/>
       <c r="S41" s="3" t="n">
-        <v>0.9</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W41" s="10" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>0</v>
+      <c r="X41" s="10" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3838,74 +3780,72 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>60.9</v>
+        <v>608.8</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="3" t="n">
-        <v>5.1</v>
+        <v>35.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>920</v>
-      </c>
+        <v>93.2</v>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
       <c r="P42" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20</v>
+        <v>26.9</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>0.9</v>
+        <v>16.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>99</v>
+        <v>949</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>0.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0</v>
+        <v>161.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10</v>
+        <v>18.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3921,82 +3861,68 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00000 0
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
+        <v>604.4</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>81</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.5</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="n">
-        <v>20.8</v>
+        <v>24.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="T43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>0.6</v>
-      </c>
       <c r="X43" s="3" t="n">
-        <v>10.9</v>
+        <v>15.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0</v>
+        <v>729.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>5</v>
+        <v>20.3</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4011,84 +3937,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>3109.5</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00000 0
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>2.2</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4103,74 +3975,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3109.5</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>22.5</v>
+        <v>3119.5</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>18.9</v>
+        <v>1181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.9</v>
+        <v>356.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>53.1</v>
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>60.9</v>
+        <v>168.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>496</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>124.8</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>126.3</v>
+        <v>1126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>0</v>
+        <v>1282.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>729.8</v>
+        <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1208.9</v>
+        <v>1108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0</v>
+        <v>1060.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>300.8</v>
+        <v>23028.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2.2</v>
+        <v>20.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4188,73 +4062,63 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>15.5</v>
+      <c r="D46" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>503.4</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>1</v>
+        <v>13.8</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="10" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>13.9</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="R46" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>208.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>8.699999999999999</v>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="10" t="n">
+        <v>865.4</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +146,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +158,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,48 +777,50 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="E4" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F4" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
+      <c r="G4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <v>10.8</v>
+      <c r="I4" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="L4" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99.8</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" s="10" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>21.1</v>
+      <c r="P4" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>89.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
@@ -835,21 +828,23 @@
       <c r="T4" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="V4" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="W4" s="10" t="n">
-        <v>17</v>
+        <v>17.8</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>4.6</v>
+        <v>10.9</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -865,33 +860,33 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1564.3</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="E5" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H5" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -901,13 +896,15 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>95.8</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -920,19 +917,19 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="W5" s="10" t="n">
-        <v>17.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -951,71 +948,73 @@
         <v>338</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>19.3</v>
+        <v>4.9</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>1141.6</v>
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>110.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>994.2</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>21562.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>1.9</v>
+        <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>44.4</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>671.8</v>
+        <v>62.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.2</v>
+        <v>18.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1103.9</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1031,52 +1030,56 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355.7</v>
-      </c>
-      <c r="D7" s="9" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>80.09999999999999</v>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.3</v>
+        <v>11.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>41.4</v>
+        <v>19.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>52.2</v>
+        <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>298.5</v>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="S7" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T7" s="3" t="n">
         <v>77</v>
       </c>
@@ -1084,14 +1087,16 @@
         <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>184</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.5</v>
@@ -1110,72 +1115,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="F8" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="H8" s="3" t="n">
-        <v>441.2</v>
+        <v>14.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>4971.2</v>
+      <c r="L8" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>31.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>99.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R8" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W8" s="10" t="n">
-        <v>917.8</v>
+      <c r="V8" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>97.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1191,68 +1200,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182528.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>126</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="9" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>161.5</v>
+        <v>61.5</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.7</v>
+        <v>19.7</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>28.9</v>
+        <v>1281.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
+        <v>423.8</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>103.3</v>
+        <v>10.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>195.6</v>
+        <v>985.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>998.8</v>
-      </c>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>910.1</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>295.3</v>
+        <v>95.5</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>194.8</v>
+        <v>949.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>19429</v>
+        <v>94290.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1268,41 +1285,49 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D10" s="9" t="n">
+        <v>3650.1</v>
+      </c>
+      <c r="D10" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="E10" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>41.2</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16.8</v>
+        <v>11.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="n">
+        <v>83.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>18</v>
@@ -1313,17 +1338,23 @@
       <c r="T10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>17.4</v>
+      </c>
       <c r="X10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>85.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>38.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1344,64 +1375,72 @@
       <c r="D11" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="E11" s="9" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>13.9</v>
+      </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="10" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="Q11" s="10" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R11" s="10" t="n">
-        <v>811.4</v>
-      </c>
-      <c r="S11" s="10" t="n">
-        <v>289.5</v>
+        <v>91.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W11" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="W11" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="X11" s="10" t="n">
-        <v>20.4</v>
+      <c r="X11" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1416,76 +1455,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>521.2</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>581.1</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S12" s="10" t="n">
-        <v>46.9</v>
+      <c r="S12" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.6</v>
+        <v>14104.6</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>23.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1501,25 +1540,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9455.6</v>
+        <v>555.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>113.8</v>
+      <c r="E13" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1528,49 +1567,47 @@
         <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>717.6</v>
+        <v>11.1</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>49.3</v>
+        <v>19.2</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>66.8</v>
+      </c>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>7.8</v>
+      <c r="W13" s="8" t="n">
+        <v>97.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1586,46 +1623,46 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>20319.9</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>441.5</v>
+      <c r="E14" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>4.5</v>
       </c>
       <c r="H14" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>12.9</v>
-      </c>
       <c r="J14" s="3" t="n">
-        <v>31.6</v>
+        <v>9.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>43.5</v>
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>820.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>84.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>929</v>
+        <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1636,22 +1673,26 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="10" t="n">
-        <v>71.8</v>
+      <c r="T14" s="3" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="W14" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>25.2</v>
+      </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1672,38 +1713,44 @@
       <c r="D15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>19.1</v>
+      <c r="E15" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>12082.1</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="L15" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P15" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>2.1</v>
+      <c r="P15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1712,18 +1759,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>948</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
+        <v>9648</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>41.2</v>
+        <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>824.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1742,47 +1793,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2326.9</v>
-      </c>
-      <c r="D16" s="12" t="n">
+        <v>23069.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>295.7</v>
+      <c r="E16" s="10" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>195481.9</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>139.7</v>
+      </c>
       <c r="J16" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>166.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>19491</v>
+        <v>481.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>1115.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1794,22 +1847,22 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>5.3</v>
+        <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10</v>
+        <v>1100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>190.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>9.9</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1825,72 +1878,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>414.5</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>824.1</v>
+        <v>4814.1</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>19.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="J17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S17" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>562.6</v>
-      </c>
-      <c r="U17" s="10" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="10" t="n">
-        <v>1.4</v>
+      <c r="V17" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="10" t="n">
-        <v>99.59999999999999</v>
+      <c r="X17" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>898</v>
+        <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>297.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1906,66 +1963,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>335.7</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E18" s="10" t="n">
+        <v>955.7</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="11" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H18" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R18" s="10" t="n">
-        <v>719</v>
+        <v>980.9</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W18" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>6.2</v>
+        <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1981,65 +2048,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
+        <v>455.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>116.26</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>19.3</v>
+        <v>25.7</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>19.93</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M19" s="10" t="n">
-        <v>13.8</v>
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>196.8</v>
+        <v>41.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.3</v>
+        <v>24.3</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>13.4</v>
+      <c r="S19" s="8" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W19" s="10" t="n">
-        <v>17.5</v>
+        <v>36.1</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>98.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>894.8</v>
+        <v>84</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2058,66 +2131,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>494.9</v>
-      </c>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="13" t="n">
-        <v>124.94</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G20" s="10" t="n">
+        <v>1494.9</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>221.4</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>3.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="10" t="n">
+      <c r="S20" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>188</v>
+      </c>
       <c r="U20" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>43.4</v>
+      <c r="W20" s="8" t="n">
+        <v>58.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>21.9</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2133,28 +2214,28 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>88.8</v>
+        <v>371.3</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>9160.799999999999</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>21.1</v>
@@ -2162,15 +2243,17 @@
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="M21" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>88.7</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>180</v>
+        <v>1808</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
@@ -2179,22 +2262,26 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
       <c r="U21" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="V21" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="10" t="n">
-        <v>169.4</v>
+      <c r="W21" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2212,19 +2299,19 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>29.5</v>
+      <c r="D22" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>19.2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H22" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2234,45 +2321,51 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M22" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P22" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="10" t="n">
+      <c r="Q22" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V22" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>36.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2289,72 +2382,74 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="10" t="n">
         <v>1128.5</v>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>4.5</v>
+      <c r="E23" s="10" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1161.4</v>
+        <v>18.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>110.9</v>
+        <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>115.9</v>
+        <v>15.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>20.5</v>
+        <v>207.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>29489</v>
+        <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1113.6</v>
+        <v>11513.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.5</v>
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2328</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1219.8</v>
+        <v>149.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>186.3</v>
+        <v>8.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>938.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9429</v>
+        <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.9</v>
+        <v>1196.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2370,63 +2465,77 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>43791.8</v>
-      </c>
-      <c r="D24" s="12" t="n">
+        <v>4972.9</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="10" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="10" t="n">
-        <v>21565.9</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="F24" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>59.7</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M24" s="10" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="8" t="n">
+        <v>18</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q24" s="10" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="S24" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="T24" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="10" t="n">
-        <v>189.4</v>
-      </c>
-      <c r="W24" s="3" t="inlineStr"/>
-      <c r="X24" s="10" t="n">
-        <v>8881.200000000001</v>
+      <c r="V24" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2441,70 +2550,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>872.6</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>13.6</v>
+        <v>253.6</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>2135.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8</v>
+        <v>81.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="X25" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2520,19 +2635,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>258.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="11" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="13" t="n">
-        <v>11.89</v>
+      <c r="F26" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.1</v>
+        <v>17.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.5</v>
@@ -2541,51 +2656,55 @@
         <v>0.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="M26" s="8" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>88808</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="10" t="n">
-        <v>15.3</v>
+      <c r="W26" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2601,46 +2720,52 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>535.8</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="E27" s="10" t="n">
+        <v>9351.700000000001</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="13" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>1312.5</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>11.7</v>
+      </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="10" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>28.1</v>
@@ -2651,15 +2776,17 @@
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="10" t="n">
-        <v>19</v>
+      <c r="V27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>88.8</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2678,61 +2805,67 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.3</v>
+        <v>331.8</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="13" t="n">
-        <v>18.17</v>
+      <c r="F28" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="8" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J28" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K28" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="M28" s="10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O28" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="10" t="n">
+      <c r="P28" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>42.2</v>
+      <c r="R28" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>4.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>41.2</v>
+      <c r="W28" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>19.2</v>
@@ -2762,65 +2895,71 @@
       <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="10" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N29" s="10" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>991</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R29" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>856.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="10" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="W29" s="10" t="n">
-        <v>1991</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+      <c r="V29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2838,68 +2977,74 @@
       <c r="C30" s="3" t="n">
         <v>1569.9</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="10" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="11" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>194.3</v>
+      <c r="F30" s="10" t="n">
+        <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1544.9</v>
+        <v>649.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1629.4</v>
+        <v>62.9</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>176.9</v>
+        <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>8.9</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>444924.4</v>
+        <v>491</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>212.1</v>
+        <v>412.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>998.9</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>9413.799999999999</v>
+        <v>4135.1</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>244.4</v>
+        <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>185.9</v>
+        <v>85.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>829.4</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>922</v>
+        <v>6548</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2917,68 +3062,70 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="D31" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="H31" s="3" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H31" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="M31" s="8" t="n">
+        <v>19.9</v>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>1454.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
+      <c r="R31" s="8" t="n">
+        <v>7.8</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>8115.4</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W31" s="10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>18.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>8010.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2996,59 +3143,73 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="13" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>282.13</v>
+      <c r="D32" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>81</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>19.6</v>
+        <v>79.3</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V32" s="3" t="inlineStr"/>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>181.7</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3068,65 +3229,71 @@
       <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="10" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F33" s="13" t="n">
+      <c r="E33" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F33" s="9" t="n">
         <v>18.17</v>
       </c>
-      <c r="G33" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="3" t="n">
+      <c r="G33" s="8" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M33" s="10" t="n">
-        <v>1097.2</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="10" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="V33" s="3" t="n">
+      <c r="Q33" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X33" s="10" t="n">
-        <v>980</v>
+      <c r="W33" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3142,68 +3309,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1144.4</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>15.1</v>
+        <v>211.4</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>15.97</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>9.6</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2.5</v>
+        <v>98.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="N34" s="3" t="n">
-        <v>18.8</v>
+        <v>91.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" s="10" t="n">
-        <v>16.9</v>
-      </c>
       <c r="W34" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X34" s="10" t="n">
-        <v>16.6</v>
+        <v>15.2</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90.8</v>
+        <v>20</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3221,26 +3396,26 @@
       <c r="C35" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D35" s="13" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="E35" s="10" t="n">
+      <c r="D35" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G35" s="10" t="n">
+      <c r="F35" s="9" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H35" s="10" t="n">
+      <c r="H35" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>9.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3248,11 +3423,11 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="10" t="n">
-        <v>21281.8</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>19.9</v>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
@@ -3261,32 +3436,34 @@
         <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>23.9</v>
+        <v>29.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T35" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>68.8</v>
+      </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>48.4</v>
+        <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>17.7</v>
+        <v>18.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3305,69 +3482,73 @@
         <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>10.9</v>
+        <v>25.7</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>105.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.3</v>
+        <v>93.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="10" t="n">
-        <v>115</v>
+      <c r="L36" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>16.4</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q36" s="10" t="n">
-        <v>27</v>
+        <v>18.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" s="10" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V36" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="X36" s="10" t="n">
-        <v>32.6</v>
+        <v>17.2</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>10.8</v>
+        <v>28.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3383,76 +3564,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>19782.4</v>
-      </c>
-      <c r="D37" s="12" t="n">
+        <v>2078.2</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>1118.4</v>
       </c>
-      <c r="E37" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>1092.2</v>
+      <c r="E37" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.9</v>
+        <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>819.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>150.1</v>
+        <v>5071.7</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1681.5</v>
+        <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>167.6</v>
+        <v>62.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>401.2</v>
+        <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>382191.4</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>233.2</v>
+        <v>93.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.9</v>
+        <v>90</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>181.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.9</v>
+        <v>429.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3470,66 +3651,74 @@
       <c r="C38" s="3" t="n">
         <v>495.6</v>
       </c>
-      <c r="D38" s="11" t="inlineStr"/>
-      <c r="E38" s="12" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="I38" s="10" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="n">
+      <c r="D38" s="10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.9</v>
+        <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S38" s="10" t="n">
-        <v>172</v>
+        <v>20.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
-      <c r="U38" s="10" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="V38" s="10" t="n">
-        <v>8101.4</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>16.3</v>
+      </c>
       <c r="X38" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>184.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>81.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3545,68 +3734,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>664.1</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="F39" s="13" t="n">
-        <v>18.15</v>
+      <c r="F39" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J39" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="10" t="n">
-        <v>2120.2</v>
+        <v>8.1</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P39" s="10" t="n">
+      <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="10" t="n">
-        <v>24.8</v>
+      <c r="Q39" s="8" t="n">
+        <v>69.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S39" s="10" t="n">
-        <v>50.5</v>
+        <v>8.9</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>521</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="10" t="n">
-        <v>98.8</v>
+      <c r="V39" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>162.8</v>
+        <v>64</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3624,17 +3821,17 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16.3</v>
+        <v>11.6</v>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="n">
@@ -3644,52 +3841,52 @@
         <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="L40" s="10" t="n">
-        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="N40" s="10" t="n">
-        <v>21.9</v>
+      <c r="N40" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q40" s="10" t="n">
-        <v>35.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0.2</v>
+        <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="10" t="n">
-        <v>22.3</v>
+      <c r="V40" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X40" s="10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>59</v>
+        <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3705,66 +3902,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>794.3</v>
-      </c>
-      <c r="D41" s="9" t="n">
+        <v>694.3</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="14" t="inlineStr"/>
-      <c r="F41" s="10" t="n">
+      <c r="E41" s="9" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="J41" s="3" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="10" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R41" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17.9</v>
+        <v>12</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="W41" s="10" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="10" t="n">
-        <v>22.8</v>
+      <c r="X41" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3780,72 +3987,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>608.8</v>
-      </c>
-      <c r="D42" s="9" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="D42" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>160.5</v>
+      <c r="E42" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.8</v>
+        <v>53.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>35.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+      <c r="L42" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N42" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="O42" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>949</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>49</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>47.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.2</v>
+        <v>28.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3861,39 +4072,45 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>604.4</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="D43" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="14" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>81</v>
+        <v>1627.9</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K43" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="3" t="n">
-        <v>434</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
+      <c r="L43" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>1021.9</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
       </c>
@@ -3904,25 +4121,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2.8</v>
       </c>
       <c r="U43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Y43" s="3" t="n">
         <v>39.9</v>
       </c>
-      <c r="V43" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>729.8</v>
-      </c>
       <c r="Z43" s="3" t="n">
-        <v>20.3</v>
+        <v>211.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3937,10 +4154,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3977,14 +4196,14 @@
       <c r="C45" s="3" t="n">
         <v>3119.5</v>
       </c>
-      <c r="D45" s="12" t="n">
-        <v>431.1</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>92.5</v>
+      <c r="D45" s="10" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>92.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -3993,58 +4212,58 @@
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1181.9</v>
+        <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>356.4</v>
+        <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>168.9</v>
+        <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>124.8</v>
+        <v>121</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1126.3</v>
+        <v>126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.2</v>
+        <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1282.2</v>
+        <v>212.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1108.9</v>
+        <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1060.9</v>
+        <v>658</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>23028.1</v>
+        <v>382.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.5</v>
+        <v>281.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4062,63 +4281,73 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>503.4</v>
+      <c r="E46" s="10" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>200.4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="10" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="M46" s="10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q46" s="10" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="R46" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>900.1</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="10" t="n">
+      <c r="S46" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="U46" s="8" t="n">
         <v>865.4</v>
       </c>
-      <c r="V46" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="V46" s="8" t="n">
+        <v>1541.6</v>
+      </c>
+      <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>181.4</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -158,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -777,13 +777,13 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="10" t="n">
         <v>25.9</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -793,7 +793,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -805,28 +805,28 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>15.7</v>
+        <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>20.2</v>
+        <v>99</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="8" t="n">
-        <v>89.3</v>
+      <c r="R4" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -834,8 +834,8 @@
       <c r="V4" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>12</v>
+      <c r="W4" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
@@ -844,7 +844,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
+        <v>14649.5</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>20.5</v>
+      <c r="F5" s="10" t="n">
+        <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>12.5</v>
@@ -884,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>14</v>
@@ -896,7 +896,7 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>95.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.4</v>
@@ -917,9 +917,9 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W5" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -929,7 +929,7 @@
         <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -947,20 +947,20 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="D6" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>110.6</v>
+      <c r="H6" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
@@ -969,23 +969,21 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.6</v>
+        <v>14.2</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>21562.1</v>
+        <v>256.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -1008,13 +1006,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,15 +1028,15 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>25.3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1057,7 +1055,7 @@
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>15.2</v>
@@ -1066,7 +1064,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1078,13 +1076,13 @@
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>7.7</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
@@ -1115,16 +1113,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.8</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>19.2</v>
+      <c r="F8" s="10" t="n">
+        <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>9</v>
@@ -1135,26 +1133,26 @@
       <c r="I8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>14.1</v>
+      <c r="J8" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>31.4</v>
+        <v>13.1</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>4.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
@@ -1171,11 +1169,11 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>29.8</v>
+      <c r="V8" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>97.8</v>
+        <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
@@ -1202,17 +1200,17 @@
       <c r="C9" s="3" t="n">
         <v>1825.2</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="E9" s="9" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1220,38 +1218,36 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>1281.9</v>
+        <v>28.9</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>423.8</v>
+        <v>422</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.3</v>
+        <v>103.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>985.6</v>
+        <v>9285.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>910.1</v>
+        <v>891.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1263,13 +1259,13 @@
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>949.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94290.8</v>
+        <v>9429.799999999999</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.7</v>
+        <v>116.9</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1290,41 +1286,41 @@
       <c r="D10" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="E10" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>41.2</v>
+        <v>12.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>58</v>
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>83.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>2</v>
@@ -1336,15 +1332,15 @@
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1373,13 +1369,13 @@
         <v>329.6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>13.9</v>
+        <v>23.9</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1394,49 +1390,49 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>12.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>52.7</v>
+        <v>5.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.6</v>
+        <v>231.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>80.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>62.3</v>
+        <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>21.9</v>
+      <c r="S11" s="8" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>15</v>
+        <v>188.6</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>28.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>99.8</v>
+        <v>98.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1</v>
@@ -1455,58 +1451,56 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>581.1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>501.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>51.7</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>53.9</v>
+      <c r="E12" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S12" s="8" t="n">
+      <c r="R12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>14104.6</v>
+        <v>18.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1524,7 +1518,7 @@
         <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1540,19 +1534,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>555.6</v>
+        <v>155.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>87.09999999999999</v>
+      <c r="E13" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1566,20 +1560,20 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>11.1</v>
+      <c r="L13" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>19.6</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1587,18 +1581,20 @@
       <c r="R13" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>19.7</v>
+      <c r="S13" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>97.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
@@ -1607,7 +1603,7 @@
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1623,9 +1619,9 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D14" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -1635,7 +1631,7 @@
         <v>19.7</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>8.9</v>
@@ -1644,10 +1640,10 @@
         <v>2.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>12.5</v>
@@ -1655,8 +1651,8 @@
       <c r="M14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>84.3</v>
+      <c r="N14" s="8" t="n">
+        <v>94.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
@@ -1674,19 +1670,19 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>171.1</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>17.8</v>
+        <v>7.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="8" t="n">
-        <v>18.4</v>
+      <c r="W14" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>25.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
@@ -1708,12 +1704,12 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>484.5</v>
+        <v>454.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="F15" s="3" t="n">
@@ -1722,11 +1718,11 @@
       <c r="G15" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>12082.1</v>
+      <c r="H15" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.4</v>
+        <v>0.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1735,13 +1731,13 @@
         <v>11.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.7</v>
+        <v>18.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
@@ -1749,7 +1745,7 @@
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1759,22 +1755,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9648</v>
-      </c>
-      <c r="U15" s="8" t="n">
+        <v>248</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.6</v>
+        <v>1.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>824.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1793,49 +1789,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>23069.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>2306.9</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F16" s="10" t="n">
+      <c r="E16" s="9" t="n">
+        <v>655.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>58.9</v>
+        <v>48.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>139.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
+        <v>134.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>481.8</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1115.7</v>
+        <v>118.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1850,16 +1846,16 @@
         <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1100.4</v>
+        <v>100.9</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>9421</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1878,19 +1874,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4814.1</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" s="10" t="n">
+        <v>814.1</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>97.09999999999999</v>
+      <c r="F17" s="9" t="n">
+        <v>19.1</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1898,23 +1894,23 @@
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>16.4</v>
+      <c r="J17" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.6</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98.8</v>
+        <v>28.6</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1925,7 +1921,7 @@
       <c r="R17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1947,7 +1943,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1965,47 +1961,45 @@
       <c r="C18" s="3" t="n">
         <v>955.7</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>0.9</v>
+      <c r="D18" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.5</v>
+        <v>25.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>182.2</v>
+        <v>18</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>980.9</v>
+        <v>982.8</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>66.40000000000001</v>
+        <v>216.8</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>19</v>
@@ -2014,25 +2008,25 @@
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2048,16 +2042,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>455.6</v>
+        <v>435.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>19.93</v>
+      <c r="E19" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>1.2</v>
@@ -2069,47 +2063,49 @@
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>14.3</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>15.5</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>41.8</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="8" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>28.9</v>
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2131,16 +2127,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1494.9</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>19.58</v>
+        <v>1497.9</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.8</v>
@@ -2149,18 +2145,18 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>14.3</v>
+        <v>2.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="M20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2168,34 +2164,34 @@
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>3.5</v>
+        <v>23.9</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>19.2</v>
+        <v>91.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>58.8</v>
+        <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>8</v>
@@ -2216,23 +2212,23 @@
       <c r="C21" s="3" t="n">
         <v>371.3</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>9160.799999999999</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="D21" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>89.5</v>
+        <v>15.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
@@ -2250,7 +2246,7 @@
         <v>88.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1808</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>8</v>
@@ -2262,25 +2258,25 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2299,17 +2295,17 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2317,39 +2313,41 @@
       <c r="I22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>21.4</v>
+        <v>1.3</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>4.6</v>
+        <v>224.6</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>18.7</v>
+        <v>185.4</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>1.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2358,7 +2356,7 @@
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>28.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2382,17 +2380,17 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>1128.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
+      <c r="D23" s="9" t="n">
+        <v>1128.4</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="9" t="n">
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
@@ -2407,49 +2405,45 @@
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>207.1</v>
+        <v>20.7</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>71.8</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>11513.6</v>
+        <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>91.8</v>
-      </c>
+        <v>918.5</v>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>3260.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
+        <v>49.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>8.6</v>
+        <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>938.9</v>
+        <v>93.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1196.3</v>
+        <v>198.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2465,58 +2459,56 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4972.9</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E24" s="10" t="n">
+        <v>4912.9</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>8.5</v>
+      <c r="H24" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>5.4</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>14.7</v>
+        <v>1.4</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>18</v>
+      <c r="N24" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>85.3</v>
+      <c r="P24" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>6.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
@@ -2524,8 +2516,8 @@
       <c r="V24" s="8" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="W24" s="8" t="n">
-        <v>73.09999999999999</v>
+      <c r="W24" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>18.7</v>
@@ -2534,7 +2526,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2550,49 +2542,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>253.6</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>15.39</v>
+        <v>223.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>2135.6</v>
+        <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>81.7</v>
+        <v>8.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>96.2</v>
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>12.1</v>
+      <c r="N25" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2601,25 +2593,25 @@
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>22</v>
+      <c r="W25" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>93.8</v>
+        <v>920.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2640,24 +2632,22 @@
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
@@ -2665,18 +2655,18 @@
         <v>15.8</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>88808</v>
+        <v>908.8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q26" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2686,7 +2676,7 @@
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2695,13 +2685,13 @@
         <v>15.6</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>11.2</v>
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.6</v>
@@ -2720,25 +2710,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9351.700000000001</v>
+        <v>435.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>1312.5</v>
-      </c>
-      <c r="H27" s="8" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="I27" s="8" t="n">
-        <v>11.7</v>
+      <c r="I27" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2747,21 +2737,21 @@
         <v>13.2</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>25.8</v>
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2770,14 +2760,12 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
@@ -2786,7 +2774,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2805,16 +2793,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.8</v>
+        <v>331.3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>11.8</v>
+      <c r="F28" s="11" t="n">
+        <v>1.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2822,8 +2810,8 @@
       <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <v>7.5</v>
+      <c r="I28" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2835,7 +2823,7 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
@@ -2856,10 +2844,10 @@
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2893,17 +2881,15 @@
         <v>309.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.7</v>
-      </c>
+        <v>23.7</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
@@ -2917,7 +2903,7 @@
         <v>0.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>15</v>
@@ -2932,7 +2918,7 @@
         <v>10.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>19</v>
@@ -2950,16 +2936,16 @@
         <v>13.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>79.40000000000001</v>
+        <v>1.5</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2977,17 +2963,17 @@
       <c r="C30" s="3" t="n">
         <v>1569.9</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="9" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>649.9</v>
+        <v>645.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>62.9</v>
@@ -2996,55 +2982,53 @@
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.9</v>
+        <v>69</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>412.1</v>
-      </c>
+        <v>491.8</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
-        <v>998.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4135.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.7</v>
+        <v>8.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>829.4</v>
+        <v>824.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6548</v>
+        <v>94228</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3062,29 +3046,29 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F31" s="10" t="n">
+      <c r="E31" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>8.1</v>
+      <c r="I31" s="8" t="n">
+        <v>81.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>15</v>
@@ -3094,38 +3078,36 @@
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>1454.4</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1644.1</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>7.8</v>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>9211.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>8010.1</v>
+        <v>8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3144,39 +3126,41 @@
         <v>364.2</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="F32" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F32" s="11" t="n">
         <v>81</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>79.3</v>
+        <v>29.1</v>
       </c>
       <c r="L32" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -3184,31 +3168,31 @@
         <v>13</v>
       </c>
       <c r="R32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
         <v>14.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.8</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>26.6</v>
+        <v>16.6</v>
       </c>
       <c r="W32" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>181.7</v>
+      <c r="X32" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3230,13 +3214,13 @@
         <v>23.7</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F33" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F33" s="11" t="n">
         <v>18.17</v>
       </c>
-      <c r="G33" s="8" t="n">
-        <v>1008</v>
+      <c r="G33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>11.5</v>
@@ -3250,14 +3234,14 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="8" t="n">
-        <v>4.9</v>
+      <c r="L33" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12.7</v>
+        <v>11.7</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>62.8</v>
+        <v>60.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3266,34 +3250,34 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>21.2</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="X33" s="8" t="n">
-        <v>87.09999999999999</v>
+      <c r="X33" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3311,17 +3295,17 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>15.97</v>
+      <c r="D34" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>57.19</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>14.2</v>
@@ -3330,28 +3314,26 @@
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>98.5</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>91.8</v>
+        <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="8" t="n">
-        <v>96.90000000000001</v>
+      <c r="Q34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
@@ -3360,22 +3342,22 @@
         <v>1.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="X34" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3394,18 +3376,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
+        <v>172.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>22.2</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="G35" s="8" t="n">
+      <c r="F35" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="H35" s="8" t="n">
@@ -3415,7 +3397,7 @@
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3426,23 +3408,21 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>29.9</v>
+        <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>68.8</v>
@@ -3450,14 +3430,14 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>81</v>
@@ -3482,22 +3462,22 @@
         <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>71.38</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>99.5</v>
+        <v>25.1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>105.9</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>93.5</v>
+        <v>3.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4.8</v>
@@ -3506,22 +3486,22 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>16.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>870.8</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3530,22 +3510,22 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>31.1</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V36" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1</v>
@@ -3566,13 +3546,13 @@
       <c r="C37" s="3" t="n">
         <v>2078.2</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="9" t="n">
         <v>1118.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3582,28 +3562,28 @@
         <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>819.4</v>
+        <v>181.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>5071.7</v>
+        <v>50.7</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
@@ -3612,13 +3592,13 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3801.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>93.2</v>
+        <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>90</v>
@@ -3630,10 +3610,10 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.9</v>
+        <v>422.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3649,31 +3629,31 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>495.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E38" s="10" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>84.90000000000001</v>
+      <c r="F38" s="9" t="n">
+        <v>18.4</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>25.1</v>
+        <v>35.1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>61.5</v>
+        <v>66.5</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>17</v>
+        <v>170.2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>13.7</v>
@@ -3685,28 +3665,28 @@
         <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="8" t="n">
-        <v>117</v>
+      <c r="R38" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>2.6</v>
+        <v>16.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>18</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>16.3</v>
@@ -3715,10 +3695,10 @@
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.2</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3734,13 +3714,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>664.1</v>
-      </c>
-      <c r="D39" s="11" t="n">
+        <v>624.4</v>
+      </c>
+      <c r="D39" s="10" t="n">
         <v>25.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3758,49 +3738,49 @@
         <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>69.8</v>
+      <c r="Q39" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>521</v>
+      <c r="S39" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>27.5</v>
+        <v>26</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="8" t="n">
         <v>62.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3821,7 +3801,7 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="10" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
@@ -3833,7 +3813,9 @@
       <c r="G40" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
@@ -3843,11 +3825,11 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12</v>
@@ -3856,16 +3838,16 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>48.9</v>
@@ -3874,7 +3856,7 @@
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>20.3</v>
+        <v>25.3</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>17.3</v>
@@ -3886,7 +3868,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3902,40 +3884,38 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>694.3</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>699.3</v>
+      </c>
+      <c r="D41" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>18.1</v>
+      <c r="E41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>98</v>
@@ -3943,35 +3923,35 @@
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>293.5</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>18.2</v>
+      <c r="Q41" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>72.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>58.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>641.7</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3987,49 +3967,49 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>208.8</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>608.8</v>
+      </c>
+      <c r="D42" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="11" t="n">
         <v>18.17</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>53.8</v>
+        <v>3.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
-        <v>11.9</v>
+      <c r="L42" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>18.1</v>
+        <v>13.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>26.7</v>
+      <c r="Q42" s="8" t="n">
+        <v>61.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
@@ -4040,8 +4020,8 @@
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="U42" s="8" t="n">
-        <v>47.4</v>
+      <c r="U42" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -4050,13 +4030,13 @@
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4072,9 +4052,9 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>5049.4</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>26.1</v>
       </c>
       <c r="E43" s="8" t="n">
@@ -4082,7 +4062,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>1627.9</v>
+        <v>127.9</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4100,16 +4080,16 @@
         <v>13</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>1021.9</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>52.1</v>
+        <v>122.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>97</v>
+        <v>972</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
@@ -4121,25 +4101,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>68</v>
+      <c r="W43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>211.9</v>
+        <v>210.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4157,7 +4137,7 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
+      <c r="D44" s="10" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
@@ -4196,14 +4176,14 @@
       <c r="C45" s="3" t="n">
         <v>3119.5</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="9" t="n">
         <v>131.9</v>
       </c>
-      <c r="E45" s="10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>92.3</v>
+      <c r="E45" s="9" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -4215,13 +4195,13 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>127.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>36.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
@@ -4230,10 +4210,10 @@
         <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>298</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4242,28 +4222,28 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>212.5</v>
+        <v>2172.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>7.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>658</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>382.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>281.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4281,20 +4261,20 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="10" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>181.5</v>
+      <c r="E46" s="9" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>81.5</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>200.4</v>
+        <v>1015.4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>3.8</v>
@@ -4302,20 +4282,20 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>1111</v>
+      <c r="K46" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>1219.8</v>
+        <v>1213.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>111.9</v>
+        <v>101.9</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>35.1</v>
+        <v>32.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>900.1</v>
+        <v>9</v>
       </c>
       <c r="P46" s="8" t="n">
         <v>24.1</v>
@@ -4324,7 +4304,7 @@
         <v>25.3</v>
       </c>
       <c r="R46" s="8" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>1.6</v>
@@ -4333,20 +4313,20 @@
         <v>59.8</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>865.4</v>
+        <v>365.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>1541.6</v>
+        <v>1841.6</v>
       </c>
       <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>69.2</v>
+        <v>21.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>181.4</v>
+        <v>18.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,10 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -804,7 +810,7 @@
       <c r="L4" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -819,7 +825,7 @@
       <c r="Q4" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="10" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -831,10 +837,10 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -904,7 +910,7 @@
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -916,10 +922,10 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -971,7 +977,7 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="11" t="n">
         <v>1.3</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -987,7 +993,7 @@
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -999,10 +1005,10 @@
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1072,7 +1078,7 @@
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1084,10 +1090,10 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1157,7 +1163,7 @@
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1169,10 +1175,10 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1219,13 +1225,13 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1237,10 +1243,10 @@
       <c r="P9" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1252,10 +1258,10 @@
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>95.5</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1307,10 +1313,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1322,10 +1328,10 @@
       <c r="P10" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="10" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1337,10 +1343,10 @@
       <c r="U10" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1407,7 +1413,7 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="11" t="n">
         <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1422,8 +1428,8 @@
       <c r="U11" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>188.6</v>
+      <c r="V11" s="10" t="n">
+        <v>18.86</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>18.9</v>
@@ -1493,7 +1499,7 @@
       <c r="Q12" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1505,7 +1511,7 @@
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="8" t="n">
@@ -1590,7 +1596,7 @@
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1675,7 +1681,7 @@
       <c r="U14" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1760,7 +1766,7 @@
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="10" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1812,13 +1818,13 @@
       <c r="J16" s="3" t="n">
         <v>134.9</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>6.8</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1830,10 +1836,10 @@
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>118.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1845,10 +1851,10 @@
       <c r="U16" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>100.9</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1900,10 +1906,10 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1915,10 +1921,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>11.8</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1930,10 +1936,10 @@
       <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1998,10 +2004,10 @@
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="R18" s="8" t="n">
+      <c r="Q18" s="11" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="R18" s="10" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2016,7 +2022,7 @@
       <c r="V18" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2086,7 +2092,7 @@
       <c r="Q19" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2101,7 +2107,7 @@
       <c r="V19" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="8" t="n">
@@ -2169,7 +2175,7 @@
       <c r="Q20" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2181,10 +2187,10 @@
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="11" t="n">
         <v>91.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="10" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2254,7 +2260,7 @@
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2269,7 +2275,7 @@
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2319,11 +2325,11 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>120.9</v>
+      <c r="M22" s="11" t="n">
+        <v>12.09</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1.4</v>
@@ -2334,11 +2340,11 @@
       <c r="P22" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q22" s="8" t="n">
-        <v>224.6</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>185.4</v>
+      <c r="Q22" s="11" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>18.54</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>1.8</v>
@@ -2352,7 +2358,7 @@
       <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="10" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2401,13 +2407,13 @@
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2417,10 +2423,10 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>918.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -2430,10 +2436,10 @@
       <c r="U23" s="3" t="n">
         <v>49.8</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2483,10 +2489,10 @@
         <v>37.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2498,10 +2504,10 @@
       <c r="P24" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2513,10 +2519,10 @@
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="9" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="10" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2583,7 +2589,7 @@
       <c r="P25" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
@@ -2598,10 +2604,10 @@
       <c r="U25" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="V25" s="8" t="n">
+      <c r="V25" s="11" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2666,7 +2672,7 @@
       <c r="P26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2739,7 +2745,7 @@
       <c r="L27" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="N27" s="8" t="n">
@@ -2751,7 +2757,7 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2834,7 +2840,7 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>19.6</v>
       </c>
       <c r="R28" s="8" t="n">
@@ -2902,7 +2908,7 @@
       <c r="K29" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="11" t="n">
         <v>3.7</v>
       </c>
       <c r="M29" s="8" t="n">
@@ -2917,7 +2923,7 @@
       <c r="P29" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="R29" s="8" t="n">
@@ -2935,7 +2941,7 @@
       <c r="V29" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2984,13 +2990,13 @@
       <c r="J30" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3000,10 +3006,10 @@
         <v>491.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3015,10 +3021,10 @@
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>824.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3070,10 +3076,10 @@
       <c r="K31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
@@ -3081,10 +3087,10 @@
         <v>1644.1</v>
       </c>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3096,10 +3102,10 @@
       <c r="U31" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="9" t="n">
         <v>16.3</v>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
@@ -3164,10 +3170,10 @@
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3179,10 +3185,10 @@
       <c r="U32" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="10" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3234,7 +3240,7 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3249,10 +3255,10 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3264,10 +3270,10 @@
       <c r="U33" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3322,7 +3328,7 @@
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
+      <c r="M34" s="12" t="inlineStr"/>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
@@ -3332,10 +3338,10 @@
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3347,10 +3353,10 @@
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="10" t="n">
         <v>16.9</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="10" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3415,10 +3421,10 @@
       <c r="P35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="8" t="n">
@@ -3430,10 +3436,10 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3488,7 +3494,7 @@
       <c r="L36" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" s="8" t="n">
@@ -3500,10 +3506,10 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3515,10 +3521,10 @@
       <c r="U36" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3567,13 +3573,13 @@
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>68.5</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3585,10 +3591,10 @@
       <c r="P37" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3600,10 +3606,10 @@
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3655,10 +3661,10 @@
       <c r="K38" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3670,10 +3676,10 @@
       <c r="P38" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>17</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3685,10 +3691,10 @@
       <c r="U38" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V38" s="8" t="n">
+      <c r="V38" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="10" t="n">
         <v>16.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3740,10 +3746,10 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3773,7 +3779,7 @@
       <c r="V39" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="11" t="n">
         <v>62.5</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3926,7 +3932,7 @@
       <c r="Q41" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="11" t="n">
         <v>72.2</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3938,8 +3944,8 @@
       <c r="U41" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>641.7</v>
+      <c r="V41" s="11" t="n">
+        <v>64.17</v>
       </c>
       <c r="W41" s="8" t="n">
         <v>16.2</v>
@@ -3993,7 +3999,7 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="11" t="n">
         <v>4.6</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -4008,7 +4014,7 @@
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="Q42" s="11" t="n">
         <v>61.7</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4060,7 +4066,7 @@
       <c r="E43" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="n">
         <v>127.9</v>
       </c>
@@ -4079,8 +4085,8 @@
       <c r="L43" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>122.7</v>
+      <c r="M43" s="11" t="n">
+        <v>12.27</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>19.9</v>
@@ -4138,25 +4144,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="10" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="12" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4197,13 +4203,13 @@
       <c r="J45" s="3" t="n">
         <v>127.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>36.4</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4215,10 +4221,10 @@
       <c r="P45" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4230,10 +4236,10 @@
       <c r="U45" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4285,10 +4291,10 @@
       <c r="K46" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="9" t="n">
         <v>1213.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="9" t="n">
         <v>101.9</v>
       </c>
       <c r="N46" s="8" t="n">
@@ -4300,10 +4306,10 @@
       <c r="P46" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="R46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4315,10 +4321,10 @@
       <c r="U46" s="8" t="n">
         <v>365.4</v>
       </c>
-      <c r="V46" s="8" t="n">
+      <c r="V46" s="9" t="n">
         <v>1841.6</v>
       </c>
-      <c r="W46" s="3" t="inlineStr"/>
+      <c r="W46" s="13" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -61,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,10 +146,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,10 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -783,20 +783,20 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>11</v>
+      <c r="H4" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>11</v>
@@ -807,40 +807,40 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="13" t="n">
         <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -850,7 +850,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -866,21 +866,21 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>14649.5</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E5" s="3" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="11" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -902,19 +902,19 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -922,20 +922,20 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="10" t="n">
-        <v>17.9</v>
+      <c r="W5" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -953,23 +953,23 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="D6" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H6" s="11" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>1.7</v>
@@ -977,14 +977,14 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>256.1</v>
+      <c r="L6" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
@@ -993,11 +993,11 @@
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>62.5</v>
@@ -1005,20 +1005,20 @@
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="9" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>93</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1034,15 +1034,15 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="D7" s="10" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1070,7 +1070,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1078,32 +1078,32 @@
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>17.2</v>
+      <c r="R7" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7.7</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="10" t="n">
+      <c r="V7" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.5</v>
+        <v>33.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1121,17 +1121,17 @@
       <c r="C8" s="3" t="n">
         <v>377.9</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1148,14 +1148,14 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="11" t="n">
         <v>13.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>12.1</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>4.1</v>
+        <v>9.9</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1163,22 +1163,22 @@
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
+        <v>182.5</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>126.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>71.3</v>
+        <v>71.5</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>99</v>
@@ -1224,54 +1224,56 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="9" t="n">
+      <c r="J9" s="3" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="12" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>8.199999999999999</v>
+      <c r="M9" s="12" t="n">
+        <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>422</v>
+        <v>95.3</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" s="12" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="12" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>9285.6</v>
+        <v>198.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.1</v>
+        <v>891.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>95.5</v>
+      <c r="V9" s="12" t="n">
+        <v>95.3</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>871.2</v>
+        <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429.799999999999</v>
+        <v>9429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>116.9</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,19 +1289,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3650.1</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.3</v>
@@ -1311,42 +1313,42 @@
         <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>19.2</v>
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="R10" s="12" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V10" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W10" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="W10" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1372,16 +1374,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>329.6</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13.3</v>
+        <v>324.6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>55.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1393,55 +1395,55 @@
         <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>231.6</v>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>13.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>91.8</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="13" t="n">
         <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>89.90000000000001</v>
+      <c r="S11" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>72</v>
+        <v>1220.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="W11" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>18.4</v>
-      </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
+        <v>93.8</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1457,74 +1459,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>501.1</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>51.7</v>
+        <v>511.1</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>25.7</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>110</v>
+      <c r="H12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>14.9</v>
+      <c r="L12" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>24.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.2</v>
+        <v>16.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>2.5</v>
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>89</v>
+        <v>281</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1540,19 +1544,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>155.6</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>26.8</v>
+      <c r="E13" s="11" t="n">
+        <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1564,49 +1568,49 @@
         <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
+        <v>98.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>29.7</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>1866.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26</v>
+        <v>726</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1625,18 +1629,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
+      <c r="F14" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1651,20 +1655,20 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>94.3</v>
+        <v>12.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1676,22 +1680,22 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>171.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="V14" s="10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>18.9</v>
+      <c r="W14" s="9" t="n">
+        <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>86.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1710,9 +1714,9 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>454.5</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>26.7</v>
       </c>
       <c r="E15" s="3" t="n">
@@ -1722,31 +1726,31 @@
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>13.6</v>
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.2</v>
+        <v>10.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L15" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="11" t="n">
         <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1761,25 +1765,25 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>31.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1800,14 +1804,14 @@
       <c r="D16" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>655.3</v>
-      </c>
-      <c r="F16" s="9" t="n">
+      <c r="E16" s="12" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1816,30 +1820,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>134.9</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>6.8</v>
+      <c r="M16" s="12" t="n">
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>493</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q16" s="9" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="R16" s="9" t="n">
+        <v>432</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="12" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1849,19 +1851,19 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>90.90000000000001</v>
+        <v>255.8</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="W16" s="12" t="n">
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9421</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1880,19 +1882,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>814.1</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E17" s="9" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>12.4</v>
+      <c r="G17" s="11" t="n">
+        <v>112.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1901,31 +1903,31 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>11.7</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M17" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="9" t="n">
-        <v>11.8</v>
+      <c r="R17" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>18.3</v>
@@ -1933,11 +1935,11 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V17" s="10" t="n">
-        <v>20.1</v>
+      <c r="U17" s="11" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>1.4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>18.2</v>
@@ -1949,7 +1951,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1965,26 +1967,28 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>955.7</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E18" s="11" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="J18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.3</v>
@@ -1992,37 +1996,37 @@
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>18</v>
+      <c r="M18" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>982.8</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>21.68</v>
-      </c>
-      <c r="R18" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="R18" s="9" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="W18" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2054,64 +2058,64 @@
         <v>25.7</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="F19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H19" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H19" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>21.8</v>
+      <c r="M19" s="11" t="n">
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.8</v>
+        <v>47</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="R19" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R19" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>12.4</v>
+      <c r="S19" s="11" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W19" s="10" t="n">
+      <c r="U19" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="W19" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="X19" s="8" t="n">
-        <v>88.90000000000001</v>
+      <c r="X19" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2133,15 +2137,15 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1497.9</v>
+        <v>1417.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="E20" s="13" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2165,42 +2169,44 @@
       <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>184.4</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R20" s="10" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="R20" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V20" s="11" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="W20" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2216,40 +2222,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>371.3</v>
+        <v>379.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F21" s="8" t="n">
+      <c r="E21" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>15.6</v>
+      <c r="G21" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>21.1</v>
+      <c r="K21" s="11" t="n">
+        <v>41.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>88.7</v>
+      <c r="M21" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
@@ -2260,8 +2266,8 @@
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>18.9</v>
+      <c r="R21" s="9" t="n">
+        <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>19.3</v>
@@ -2270,21 +2276,23 @@
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="10" t="n">
-        <v>16.9</v>
+      <c r="W21" s="9" t="n">
+        <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>918.1</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2304,14 +2312,14 @@
       <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>29.3</v>
+      <c r="E22" s="13" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>19.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.7</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2325,44 +2333,44 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>12.09</v>
+      <c r="M22" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97</v>
+        <v>297</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q22" s="11" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>18.54</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8.9</v>
+        <v>59.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="9" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2386,70 +2394,72 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>1128.4</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="12" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="E23" s="12" t="n">
         <v>66.8</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M23" s="9" t="n">
+      <c r="K23" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>71.8</v>
+        <v>7.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="9" t="n">
+      <c r="P23" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q23" s="12" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>918.5</v>
+      <c r="R23" s="12" t="n">
+        <v>191.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>3260.6</v>
+        <v>232.8</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="V23" s="9" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="V23" s="12" t="n">
         <v>94.3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.8</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>198.3</v>
+        <v>116.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2465,74 +2475,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4912.9</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E24" s="9" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E24" s="12" t="n">
         <v>13.4</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>10.5</v>
+      <c r="G24" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>37.1</v>
+        <v>13.7</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" s="9" t="n">
+      <c r="L24" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="8" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Q24" s="9" t="n">
+      <c r="P24" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="W24" s="10" t="n">
+      <c r="V24" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W24" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2548,49 +2558,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>223.6</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F25" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H25" s="11" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.2</v>
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>18.4</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>18.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2602,22 +2612,22 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="V25" s="11" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="W25" s="11" t="n">
-        <v>0.1</v>
+        <v>27.9</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>12.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>920.8</v>
+        <v>92</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>12.8</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2633,56 +2643,58 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>268.3</v>
-      </c>
-      <c r="D26" s="3" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="D26" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2.2</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>908.8</v>
+        <v>108</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Q26" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S26" s="11" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2690,18 +2702,14 @@
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2716,25 +2724,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.8</v>
-      </c>
-      <c r="D27" s="3" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>131.2</v>
+      <c r="G27" s="11" t="n">
+        <v>12.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2742,14 +2750,14 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="L27" s="13" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2757,7 +2765,7 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2766,14 +2774,16 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2801,14 +2811,14 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>1.8</v>
+      <c r="F28" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2817,7 +2827,7 @@
         <v>11.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2829,36 +2839,36 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="11" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1.8</v>
+        <v>48.1</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2884,19 +2894,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.1</v>
-      </c>
-      <c r="D29" s="3" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H29" s="11" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2909,43 +2921,43 @@
         <v>0.6</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M29" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M29" s="11" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q29" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="11" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.4</v>
+        <v>1.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="W29" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+      <c r="V29" s="11" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="W29" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X29" s="11" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
@@ -2967,53 +2979,53 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1569.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="12" t="n">
         <v>71.90000000000001</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>645.9</v>
+        <v>44.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="L30" s="9" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="M30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>69</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491.8</v>
+        <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="9" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="12" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -3021,20 +3033,20 @@
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="12" t="n">
         <v>8.5</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>824.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>94228</v>
+        <v>9428</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3053,9 +3065,9 @@
         <v>314</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E31" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="F31" s="9" t="n">
@@ -3067,53 +3079,57 @@
       <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>81.5</v>
+      <c r="I31" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L31" s="9" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="n">
-        <v>1644.1</v>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R31" s="9" t="n">
-        <v>17.8</v>
+      <c r="R31" s="12" t="n">
+        <v>87.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>9211.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="9" t="n">
-        <v>8</v>
+        <v>1.1</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3131,38 +3147,38 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>81</v>
+      <c r="D32" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>27.5</v>
+        <v>39.1</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>9</v>
@@ -3170,35 +3186,31 @@
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q32" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="R32" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="Q32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="U32" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V32" s="10" t="n">
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3219,35 +3231,35 @@
       <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="11" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>18.17</v>
+      <c r="F33" s="13" t="n">
+        <v>81.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="11" t="n">
-        <v>1.5</v>
+      <c r="L33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>60.1</v>
+        <v>17.2</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>9161.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3255,35 +3267,35 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>71.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V33" s="10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>2880.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.1</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3301,69 +3313,71 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>57.19</v>
+      <c r="D34" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
+      <c r="M34" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R34" s="10" t="n">
+      <c r="Q34" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="R34" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>1.7</v>
+        <v>97.5</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="10" t="n">
+      <c r="V34" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="W34" s="10" t="n">
+      <c r="W34" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3382,21 +3396,21 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>172.8</v>
+        <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3411,45 +3425,47 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="11" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q35" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q35" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="8" t="n">
-        <v>15.9</v>
+      <c r="S35" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>68.8</v>
+        <v>60.8</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.4</v>
+        <v>128.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3470,17 +3486,17 @@
       <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3491,50 +3507,50 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="L36" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>66.40000000000001</v>
+      <c r="M36" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>870.8</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="R36" s="10" t="n">
+      <c r="Q36" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V36" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="10" t="n">
+      <c r="W36" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>26.8</v>
+        <v>114.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3552,75 +3568,73 @@
       <c r="C37" s="3" t="n">
         <v>2078.2</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>92.2</v>
+      <c r="D37" s="12" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>292.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.3</v>
+        <v>352.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>181.4</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>67.59999999999999</v>
+        <v>12.1</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>507.9</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.1</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Q37" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>89.90000000000001</v>
+      <c r="R37" s="12" t="n">
+        <v>59.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3801.9</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="W37" s="10" t="n">
+      <c r="V37" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="W37" s="9" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>422.2</v>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v>19.6</v>
-      </c>
+        <v>429.8</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3637,74 +3651,74 @@
       <c r="C38" s="3" t="n">
         <v>415.6</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>170.2</v>
+      <c r="G38" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>17</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>12.9</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="12" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>41.4</v>
+        <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q38" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Q38" s="12" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="S38" s="8" t="n">
+      <c r="R38" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V38" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="3" t="n">
+      <c r="X38" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3720,13 +3734,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.4</v>
-      </c>
-      <c r="D39" s="10" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>11.1</v>
+      <c r="E39" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3738,22 +3752,22 @@
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M39" s="11" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M39" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3761,14 +3775,14 @@
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>14.8</v>
+      <c r="Q39" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3776,20 +3790,20 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>62.5</v>
+      <c r="V39" s="13" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>16.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3807,20 +3821,20 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>11.6</v>
+      <c r="G40" s="11" t="n">
+        <v>65.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.3</v>
+        <v>15.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
@@ -3844,27 +3858,27 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q40" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.9</v>
+        <v>1948.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3874,7 +3888,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3890,74 +3904,72 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>699.3</v>
-      </c>
-      <c r="D41" s="10" t="n">
+        <v>644.3</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>87.09999999999999</v>
+      <c r="E41" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>1.2</v>
+      <c r="L41" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>18.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="11" t="n">
-        <v>72.2</v>
+      <c r="R41" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>947</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="W41" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W41" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>1.5</v>
+      <c r="X41" s="11" t="n">
+        <v>88.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3975,74 +3987,72 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>18.17</v>
+      <c r="E42" s="13" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>81.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.1</v>
+        <v>10</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="11" t="n">
-        <v>61.7</v>
+      <c r="Q42" s="9" t="n">
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4058,17 +4068,19 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5049.4</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>604.4</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="F43" s="11" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G43" s="3" t="n">
-        <v>127.9</v>
+        <v>13.7</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4082,50 +4094,50 @@
       <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>13</v>
+      <c r="L43" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>19.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>16.5</v>
+        <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W43" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V43" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W43" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>12.1</v>
+      <c r="X43" s="11" t="n">
+        <v>120.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.8</v>
+        <v>239.2</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>210.9</v>
+        <v>113</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4143,26 +4155,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="10" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="12" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr"/>
+      <c r="M44" s="15" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
-      <c r="R44" s="12" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="inlineStr"/>
-      <c r="W44" s="12" t="inlineStr"/>
+      <c r="V44" s="15" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4183,16 +4195,16 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>131.9</v>
-      </c>
-      <c r="E45" s="9" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="E45" s="12" t="n">
         <v>53.6</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="12" t="n">
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
@@ -4201,52 +4213,52 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>55.9</v>
+        <v>23.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>155.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>61.9</v>
+        <v>161.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>298</v>
+        <v>9498</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="12" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="12" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>81.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2172.5</v>
+        <v>282.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V45" s="9" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V45" s="12" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>88.09999999999999</v>
+      <c r="W45" s="12" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>10688.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>302.8</v>
+        <v>2302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4267,17 +4279,17 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="9" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>1015.4</v>
+      <c r="E46" s="12" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>51.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4286,53 +4298,55 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L46" s="9" t="n">
-        <v>1213.8</v>
-      </c>
-      <c r="M46" s="9" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>32.1</v>
+        <v>15.5</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>1111.9</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P46" s="8" t="n">
-        <v>24.1</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>12.8</v>
+      <c r="R46" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.6</v>
+        <v>11.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>365.4</v>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v>1841.6</v>
-      </c>
-      <c r="W46" s="13" t="inlineStr"/>
+        <v>58.5</v>
+      </c>
+      <c r="U46" s="11" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>16.6</v>
+      </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.8</v>
+        <v>161.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,19 +161,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,11 +792,11 @@
       <c r="G4" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="11" t="n">
-        <v>10.8</v>
+      <c r="H4" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -807,25 +804,25 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="13" t="n">
-        <v>1.5</v>
+      <c r="M4" s="9" t="n">
+        <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="R4" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -837,7 +834,7 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="W4" s="9" t="n">
@@ -850,7 +847,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -880,7 +877,7 @@
       <c r="G5" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -895,26 +892,26 @@
       <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -922,7 +919,7 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="W5" s="9" t="n">
@@ -935,7 +932,7 @@
         <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -962,10 +959,10 @@
       <c r="F6" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
@@ -975,13 +972,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="13" t="n">
-        <v>94.2</v>
+      <c r="M6" s="9" t="n">
+        <v>14.2</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>16.1</v>
@@ -990,29 +987,29 @@
         <v>99</v>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>22.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29</v>
+        <v>20.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>76</v>
@@ -1063,23 +1060,23 @@
       <c r="L7" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>12.2</v>
+      <c r="R7" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
@@ -1090,20 +1087,20 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1131,7 +1128,7 @@
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1140,7 +1137,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1148,8 +1145,8 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>13.1</v>
+      <c r="M8" s="9" t="n">
+        <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.1</v>
@@ -1158,24 +1155,24 @@
         <v>9.9</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="W8" s="9" t="n">
@@ -1204,7 +1201,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182.5</v>
+        <v>1825.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>126.5</v>
@@ -1225,43 +1222,43 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="K9" s="12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="10" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="9" t="n">
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="9" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="9" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>198.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.8</v>
+        <v>895.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="12" t="n">
-        <v>95.3</v>
+      <c r="V9" s="9" t="n">
+        <v>95.5</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>87.2</v>
@@ -1270,7 +1267,7 @@
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1310,15 +1307,15 @@
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1330,10 +1327,10 @@
       <c r="P10" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1345,8 +1342,8 @@
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>191.4</v>
+      <c r="V10" s="9" t="n">
+        <v>19.1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>17.4</v>
@@ -1379,11 +1376,11 @@
       <c r="D11" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>55.3</v>
+      <c r="E11" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1397,17 +1394,17 @@
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>13.6</v>
+      <c r="L11" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>99</v>
@@ -1415,35 +1412,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="13" t="n">
-        <v>2.3</v>
+      <c r="Q11" s="9" t="n">
+        <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1220.4</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V11" s="13" t="n">
-        <v>15.86</v>
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>18.6</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>18.9</v>
+        <v>26.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1459,7 +1456,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>11.1</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.7</v>
@@ -1477,30 +1474,30 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>24.4</v>
+      <c r="L12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q12" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1515,7 +1512,7 @@
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="9" t="n">
@@ -1525,10 +1522,10 @@
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1549,7 +1546,7 @@
       <c r="D13" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1562,7 +1559,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1570,22 +1567,22 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="L13" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q13" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1595,12 +1592,12 @@
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1866.8</v>
+        <v>66.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W13" s="9" t="n">
@@ -1610,7 +1607,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>726</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1629,7 +1626,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>331.9</v>
+        <v>531.1</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>26.8</v>
@@ -1637,7 +1634,7 @@
       <c r="E14" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1647,7 +1644,7 @@
         <v>8.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>3.6</v>
@@ -1655,22 +1652,22 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="9" t="n">
         <v>12.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q14" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1685,17 +1682,17 @@
       <c r="U14" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1720,7 +1717,7 @@
         <v>26.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.4</v>
@@ -1732,30 +1729,30 @@
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="11" t="n">
-        <v>14.9</v>
+      <c r="M15" s="9" t="n">
+        <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1770,7 +1767,7 @@
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="9" t="n">
@@ -1780,7 +1777,7 @@
         <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1799,19 +1796,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2306.9</v>
+        <v>230.6</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="10" t="n">
         <v>65.2</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="10" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1820,53 +1817,53 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K16" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K16" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="10" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="10" t="n">
         <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>432</v>
+        <v>95</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="12" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>92.90000000000001</v>
+      <c r="Q16" s="9" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>13</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>255.8</v>
-      </c>
-      <c r="V16" s="12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="12" t="n">
-        <v>190.9</v>
+      <c r="W16" s="9" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>24</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1882,19 +1879,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>461.4</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" s="12" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>112.4</v>
+      <c r="G17" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1905,13 +1902,13 @@
       <c r="J17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K17" s="11" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M17" s="12" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M17" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1923,10 +1920,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="Q17" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1935,11 +1932,11 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="11" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>1.4</v>
+      <c r="U17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>18.2</v>
@@ -1969,10 +1966,10 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="D18" s="9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>14.3</v>
       </c>
       <c r="F18" s="9" t="n">
@@ -1993,14 +1990,14 @@
       <c r="K18" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M18" s="9" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>98</v>
@@ -2008,8 +2005,8 @@
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="11" t="n">
-        <v>10.4</v>
+      <c r="Q18" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>19</v>
@@ -2018,12 +2015,12 @@
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W18" s="9" t="n">
@@ -2052,12 +2049,12 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>13</v>
       </c>
       <c r="F19" s="9" t="n">
@@ -2066,26 +2063,26 @@
       <c r="G19" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>11.8</v>
+      <c r="M19" s="9" t="n">
+        <v>12.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2093,14 +2090,14 @@
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+      <c r="Q19" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
@@ -2108,7 +2105,7 @@
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="W19" s="9" t="n">
@@ -2137,13 +2134,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1417.9</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>12.54</v>
+        <v>17.9</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>12.4</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>19.8</v>
@@ -2163,14 +2160,14 @@
       <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2178,8 +2175,8 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="3" t="n">
-        <v>13.4</v>
+      <c r="Q20" s="9" t="n">
+        <v>23.4</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>17.5</v>
@@ -2188,13 +2185,13 @@
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>12.2</v>
+        <v>12</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v>19.2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>17.7</v>
@@ -2203,7 +2200,7 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.9</v>
@@ -2222,12 +2219,12 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E21" s="11" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E21" s="9" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="9" t="n">
@@ -2243,27 +2240,27 @@
         <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L21" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L21" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="9" t="n">
@@ -2278,20 +2275,20 @@
       <c r="U21" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>16.6</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>918.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2309,11 +2306,11 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="13" t="n">
-        <v>11.32</v>
+      <c r="E22" s="9" t="n">
+        <v>13.1</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>19.5</v>
@@ -2331,39 +2328,39 @@
         <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M22" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M22" s="9" t="n">
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="9" t="n">
@@ -2392,12 +2389,12 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2089.4</v>
-      </c>
-      <c r="D23" s="12" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>128.2</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="9" t="n">
         <v>66.8</v>
       </c>
       <c r="F23" s="9" t="n">
@@ -2415,13 +2412,13 @@
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="K23" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="M23" s="12" t="n">
+      <c r="L23" s="9" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="M23" s="10" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2431,22 +2428,22 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Q23" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="12" t="n">
-        <v>191.5</v>
+      <c r="R23" s="9" t="n">
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>232.8</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="V23" s="12" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="V23" s="9" t="n">
         <v>94.3</v>
       </c>
       <c r="W23" s="9" t="n">
@@ -2456,10 +2453,10 @@
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2475,34 +2472,36 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>417.9</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E24" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H24" s="11" t="n">
+      <c r="G24" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2514,7 +2513,7 @@
       <c r="P24" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="9" t="n">
         <v>23.1</v>
       </c>
       <c r="R24" s="9" t="n">
@@ -2524,12 +2523,12 @@
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>15.4</v>
+        <v>25.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="12" t="n">
+      <c r="V24" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W24" s="9" t="n">
@@ -2558,13 +2557,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>233.5</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>13.3</v>
+      <c r="E25" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>19.3</v>
@@ -2572,7 +2571,7 @@
       <c r="G25" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
@@ -2582,13 +2581,13 @@
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L25" s="11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
+      <c r="M25" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>18.8</v>
@@ -2600,9 +2599,9 @@
         <v>0.4</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="R25" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2612,10 +2611,10 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V25" s="11" t="n">
-        <v>27.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>17</v>
@@ -2624,7 +2623,7 @@
         <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>1</v>
@@ -2643,12 +2642,12 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>228.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="9" t="n">
         <v>15.3</v>
       </c>
       <c r="F26" s="9" t="n">
@@ -2658,7 +2657,7 @@
         <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
@@ -2672,34 +2671,34 @@
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="11" t="n">
+      <c r="M26" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S26" s="11" t="n">
+      <c r="R26" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="9" t="n">
         <v>15.6</v>
       </c>
       <c r="W26" s="9" t="n">
@@ -2724,25 +2723,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.6</v>
+        <v>35.6</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>12.2</v>
+      <c r="G27" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2750,14 +2749,14 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="13" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>15.4</v>
+      <c r="L27" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>13.4</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2768,26 +2767,26 @@
       <c r="Q27" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="9" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2814,7 +2813,7 @@
       <c r="D28" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="F28" s="9" t="n">
@@ -2830,7 +2829,7 @@
         <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>32.8</v>
@@ -2838,14 +2837,14 @@
       <c r="L28" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
@@ -2853,19 +2852,19 @@
       <c r="Q28" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="9" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>48.1</v>
+        <v>78</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="W28" s="9" t="n">
@@ -2894,12 +2893,12 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.7</v>
+        <v>309.1</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E29" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E29" s="9" t="n">
         <v>14</v>
       </c>
       <c r="F29" s="9" t="n">
@@ -2908,7 +2907,7 @@
       <c r="G29" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2918,19 +2917,19 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="M29" s="9" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.2</v>
@@ -2938,29 +2937,29 @@
       <c r="Q29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="9" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.1</v>
+        <v>19.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>6.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>35.8</v>
+      <c r="V29" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X29" s="11" t="n">
+      <c r="X29" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2979,12 +2978,12 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D30" s="12" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
       <c r="F30" s="9" t="n">
@@ -3002,39 +3001,39 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="K30" s="10" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="L30" s="10" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="M30" s="9" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="9" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R30" s="12" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="R30" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>413.1</v>
+        <v>13.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="12" t="n">
-        <v>8.5</v>
+      <c r="V30" s="10" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>82.40000000000001</v>
@@ -3043,10 +3042,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9428</v>
+        <v>475</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3067,14 +3066,14 @@
       <c r="D31" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3086,37 +3085,37 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="M31" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>60.4</v>
+        <v>22.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>87.8</v>
+      <c r="R31" s="9" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V31" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>17</v>
       </c>
       <c r="W31" s="9" t="n">
@@ -3129,7 +3128,7 @@
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3145,56 +3144,56 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D32" s="11" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="E32" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>81.90000000000001</v>
+      <c r="E32" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="11" t="n">
-        <v>19.5</v>
+      <c r="R32" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="9" t="n">
@@ -3204,13 +3203,13 @@
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3226,21 +3225,21 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>11.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="13" t="n">
-        <v>81.7</v>
+      <c r="F33" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="H33" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
@@ -3249,17 +3248,17 @@
       <c r="J33" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M33" s="3" t="n">
+      <c r="L33" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M33" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="11" t="n">
-        <v>9161.9</v>
+      <c r="N33" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3267,20 +3266,20 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.6</v>
+        <v>0.2</v>
       </c>
       <c r="V33" s="9" t="n">
         <v>17.8</v>
@@ -3289,13 +3288,13 @@
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2880.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3319,11 +3318,11 @@
       <c r="E34" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14.2</v>
@@ -3334,14 +3333,14 @@
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L34" s="3" t="n">
+      <c r="K34" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L34" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>5.1</v>
+      <c r="M34" s="9" t="n">
+        <v>11.5</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
@@ -3350,25 +3349,25 @@
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="R34" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>97.5</v>
+        <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>15.2</v>
@@ -3377,10 +3376,10 @@
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3396,15 +3395,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
+        <v>77.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3419,13 +3418,13 @@
       <c r="J35" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="9" t="n">
         <v>12.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3437,23 +3436,23 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>16.5</v>
@@ -3465,7 +3464,7 @@
         <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>128.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3481,22 +3480,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>613.2</v>
+        <v>13.2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3504,38 +3503,38 @@
       <c r="J36" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="R36" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.8</v>
@@ -3547,10 +3546,10 @@
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>114.8</v>
+        <v>71.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3566,55 +3565,55 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2078.2</v>
-      </c>
-      <c r="D37" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="10" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>292.2</v>
+      <c r="F37" s="9" t="n">
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>352.3</v>
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>507.9</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>68.59999999999999</v>
+      <c r="K37" s="9" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q37" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="12" t="n">
-        <v>59.9</v>
+      <c r="R37" s="9" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>380.9</v>
@@ -3622,7 +3621,7 @@
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="12" t="n">
+      <c r="V37" s="10" t="n">
         <v>70</v>
       </c>
       <c r="W37" s="9" t="n">
@@ -3632,7 +3631,7 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.8</v>
+        <v>429.5</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3649,52 +3648,52 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>415.6</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="10" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H38" s="11" t="n">
+      <c r="H38" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I38" s="11" t="n">
-        <v>17</v>
+      <c r="I38" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="M38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Q38" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="12" t="n">
-        <v>97</v>
+      <c r="R38" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17.6</v>
@@ -3711,11 +3710,11 @@
       <c r="W38" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="11" t="n">
+      <c r="X38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>3.1</v>
@@ -3734,15 +3733,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
+        <v>24.3</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>25.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3752,34 +3751,34 @@
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M39" s="13" t="n">
-        <v>1.8</v>
+      <c r="M39" s="14" t="n">
+        <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>8.4</v>
+      <c r="R39" s="9" t="n">
+        <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>0.1</v>
@@ -3790,11 +3789,11 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="13" t="n">
-        <v>71.5</v>
+      <c r="V39" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>16.5</v>
@@ -3819,30 +3818,30 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
+        <v>37.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="11" t="n">
-        <v>65.3</v>
+      <c r="G40" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
@@ -3858,24 +3857,24 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="W40" s="9" t="n">
@@ -3909,10 +3908,10 @@
       <c r="D41" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="E41" s="14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F41" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3921,22 +3920,22 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N41" s="11" t="n">
-        <v>18.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3944,29 +3943,29 @@
       <c r="Q41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.1</v>
+        <v>22.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>947</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>21.7</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>88.8</v>
+      <c r="X41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>16.8</v>
@@ -3990,11 +3989,11 @@
       <c r="D42" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>81.7</v>
+      <c r="E42" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>16.5</v>
@@ -4003,33 +4002,33 @@
         <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>5.9</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N42" s="11" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18.2</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="R42" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -4037,16 +4036,16 @@
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
@@ -4076,7 +4075,7 @@
       <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4089,22 +4088,22 @@
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>5.4</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="11" t="n">
-        <v>19.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.6</v>
@@ -4112,7 +4111,7 @@
       <c r="Q43" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4122,22 +4121,22 @@
         <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V43" s="11" t="n">
-        <v>22.4</v>
+        <v>14.9</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>21.4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="11" t="n">
-        <v>120.9</v>
+      <c r="X43" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>239.2</v>
+        <v>29.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4156,24 +4155,24 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" s="15" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="15" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
       <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
@@ -4192,73 +4191,73 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
+        <v>119.5</v>
       </c>
       <c r="D45" s="9" t="n">
         <v>131.1</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="10" t="n">
         <v>53.6</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="9" t="n">
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" s="12" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>56.4</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>155.9</v>
+      <c r="M45" s="10" t="n">
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>161.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>9498</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="12" t="n">
+      <c r="R45" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>282.5</v>
+        <v>252.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V45" s="12" t="n">
+      <c r="V45" s="9" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="12" t="n">
+      <c r="W45" s="9" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>10688.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2302.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4282,14 +4281,14 @@
       <c r="D46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="F46" s="12" t="n">
+      <c r="E46" s="10" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>51.3</v>
+      <c r="G46" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4298,22 +4297,22 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="L46" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>11111111</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="M46" s="10" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.4</v>
@@ -4321,19 +4320,19 @@
       <c r="Q46" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="12" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.9</v>
+        <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="11" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V46" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="W46" s="9" t="n">
@@ -4343,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>10.1</v>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,13 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -780,13 +768,13 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -807,7 +795,7 @@
       <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -819,10 +807,10 @@
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -834,10 +822,10 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -847,7 +835,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -865,13 +853,13 @@
       <c r="C5" s="3" t="n">
         <v>464.5</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -892,7 +880,7 @@
       <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -904,10 +892,10 @@
       <c r="P5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -919,10 +907,10 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -950,13 +938,13 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -977,7 +965,7 @@
       <c r="L6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -987,25 +975,25 @@
         <v>99</v>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.5</v>
+        <v>67.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1033,13 +1021,13 @@
       <c r="C7" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1060,22 +1048,22 @@
       <c r="L7" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1087,10 +1075,10 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1118,13 +1106,13 @@
       <c r="C8" s="3" t="n">
         <v>377.9</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1145,22 +1133,22 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>17.1</v>
+        <v>171.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1172,10 +1160,10 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1203,13 +1191,13 @@
       <c r="C9" s="3" t="n">
         <v>1825.2</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>71.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1224,50 +1212,50 @@
       <c r="J9" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>93</v>
+        <v>493</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>895.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95.5</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1288,13 +1276,13 @@
       <c r="C10" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1309,28 +1297,28 @@
       <c r="J10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>1100.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="K10" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1342,17 +1330,17 @@
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.8</v>
+        <v>86.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1373,11 +1361,11 @@
       <c r="C11" s="3" t="n">
         <v>324.6</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>23.3</v>
+      <c r="E11" s="8" t="n">
+        <v>13.3</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>15.3</v>
@@ -1398,9 +1386,9 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M11" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1412,14 +1400,14 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
@@ -1427,14 +1415,14 @@
       <c r="U11" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>26.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>95</v>
@@ -1456,12 +1444,12 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="F12" s="3" t="n">
@@ -1485,19 +1473,19 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1507,15 +1495,15 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1543,10 +1531,10 @@
       <c r="C13" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1570,7 +1558,7 @@
       <c r="L13" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1580,9 +1568,9 @@
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q13" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1597,17 +1585,17 @@
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1628,10 +1616,10 @@
       <c r="C14" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="F14" s="3" t="n">
@@ -1655,11 +1643,11 @@
       <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="9" t="n">
-        <v>12.7</v>
+      <c r="M14" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
@@ -1667,7 +1655,7 @@
       <c r="P14" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1682,10 +1670,10 @@
       <c r="U14" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1713,23 +1701,23 @@
       <c r="C15" s="3" t="n">
         <v>484.5</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>21.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1740,7 +1728,7 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1752,7 +1740,7 @@
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1767,10 +1755,10 @@
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1798,13 +1786,13 @@
       <c r="C16" s="3" t="n">
         <v>230.6</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="8" t="n">
         <v>65.2</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="9" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1819,48 +1807,48 @@
       <c r="J16" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="8" t="n">
         <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>95</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>118.7</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>13</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="8" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>24</v>
+        <v>424</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1879,15 +1867,15 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51.4</v>
+        <v>461.4</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E17" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1905,10 +1893,10 @@
       <c r="K17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1920,10 +1908,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1935,10 +1923,10 @@
       <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1966,13 +1954,13 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1987,28 +1975,28 @@
       <c r="J18" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2020,10 +2008,10 @@
       <c r="U18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2049,15 +2037,15 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>2135.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2072,17 +2060,17 @@
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L19" s="9" t="n">
+      <c r="K19" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="9" t="n">
-        <v>12.8</v>
+      <c r="M19" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2090,10 +2078,10 @@
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2105,10 +2093,10 @@
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2134,15 +2122,15 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2157,17 +2145,17 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>19.2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2175,10 +2163,10 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2190,10 +2178,10 @@
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2221,13 +2209,13 @@
       <c r="C21" s="3" t="n">
         <v>371.3</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E21" s="9" t="n">
+      <c r="D21" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2242,13 +2230,13 @@
       <c r="J21" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2260,10 +2248,10 @@
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2275,17 +2263,17 @@
       <c r="U21" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.4</v>
@@ -2306,13 +2294,13 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2327,17 +2315,17 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>14.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2345,10 +2333,10 @@
       <c r="P22" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2360,10 +2348,10 @@
       <c r="U22" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2389,15 +2377,15 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>208.9</v>
+        <v>2089.4</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>128.2</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -2410,15 +2398,15 @@
         <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>70.7</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2430,10 +2418,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -2443,17 +2431,17 @@
       <c r="U23" s="3" t="n">
         <v>49.8</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>16.3</v>
@@ -2472,15 +2460,15 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>17.9</v>
+        <v>417.9</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2496,16 +2484,16 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>14.7</v>
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2513,25 +2501,25 @@
       <c r="P24" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>25.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2541,7 +2529,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2557,15 +2545,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.5</v>
-      </c>
-      <c r="D25" s="9" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2580,17 +2568,17 @@
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="8" t="n">
         <v>6.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2598,10 +2586,10 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2611,12 +2599,12 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V25" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="W25" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2644,17 +2632,17 @@
       <c r="C26" s="3" t="n">
         <v>268.3</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7.1</v>
+        <v>71.2</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2665,17 +2653,17 @@
       <c r="J26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2683,10 +2671,10 @@
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2698,10 +2686,10 @@
       <c r="U26" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
@@ -2723,15 +2711,15 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2746,13 +2734,13 @@
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2764,10 +2752,10 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2779,14 +2767,14 @@
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2810,13 +2798,13 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2831,13 +2819,13 @@
       <c r="J28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="8" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2849,25 +2837,25 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2895,13 +2883,13 @@
       <c r="C29" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2916,13 +2904,13 @@
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+      <c r="K29" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M29" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2934,14 +2922,14 @@
       <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>66.09999999999999</v>
@@ -2949,11 +2937,11 @@
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>15.5</v>
+      <c r="W29" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>17.4</v>
@@ -2981,12 +2969,12 @@
         <v>156.9</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>1168.2</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -3001,38 +2989,38 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>13.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="10" t="n">
+      <c r="V30" s="9" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
@@ -3042,7 +3030,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>5.4</v>
@@ -3064,16 +3052,16 @@
         <v>314</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>18.9</v>
+        <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3085,14 +3073,14 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>15</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>14.9</v>
+        <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>22.8</v>
@@ -3100,23 +3088,23 @@
       <c r="P31" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>17</v>
+        <v>170.4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
@@ -3146,14 +3134,14 @@
       <c r="C32" s="3" t="n">
         <v>364.6</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>20.7</v>
+      <c r="D32" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>18.5</v>
+      <c r="F32" s="10" t="n">
+        <v>181.5</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
@@ -3167,28 +3155,28 @@
       <c r="J32" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="K32" s="9" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="L32" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>11.1</v>
+      <c r="K32" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -3196,10 +3184,10 @@
         <v>18</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3209,7 +3197,7 @@
         <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3225,15 +3213,15 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D33" s="3" t="n">
+        <v>411.2</v>
+      </c>
+      <c r="D33" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3248,13 +3236,13 @@
       <c r="J33" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3266,10 +3254,10 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3279,22 +3267,22 @@
         <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V33" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3312,13 +3300,13 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3333,43 +3321,43 @@
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L34" s="9" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>11.5</v>
+      <c r="L34" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>115</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>29.1</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3379,7 +3367,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3395,15 +3383,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3418,13 +3406,13 @@
       <c r="J35" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3436,14 +3424,14 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>8.9</v>
+        <v>27.9</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3451,10 +3439,10 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3480,15 +3468,15 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="D36" s="3" t="n">
+        <v>613.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3503,43 +3491,43 @@
       <c r="J36" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>54.1</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3565,19 +3553,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="D37" s="8" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>66.09999999999999</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>52.3</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3591,10 +3579,10 @@
       <c r="K37" s="9" t="n">
         <v>50.1</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="8" t="n">
         <v>68.5</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="9" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3604,27 +3592,27 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3809.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="W37" s="9" t="n">
+      <c r="V37" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3648,12 +3636,12 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="F38" s="9" t="n">
@@ -3672,9 +3660,9 @@
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="M38" s="9" t="n">
@@ -3689,10 +3677,10 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3704,10 +3692,10 @@
       <c r="U38" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3733,15 +3721,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3756,32 +3744,32 @@
       <c r="J39" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M39" s="14" t="n">
+      <c r="M39" s="10" t="n">
         <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R39" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3789,10 +3777,10 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3818,15 +3806,15 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D40" s="9" t="n">
+        <v>637.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3841,7 +3829,7 @@
       <c r="J40" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
@@ -3857,16 +3845,16 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>48</v>
@@ -3874,10 +3862,10 @@
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3905,13 +3893,13 @@
       <c r="C41" s="3" t="n">
         <v>644.3</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="E41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3922,7 +3910,7 @@
       <c r="J41" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
@@ -3932,18 +3920,18 @@
         <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3955,10 +3943,10 @@
       <c r="U41" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -3986,13 +3974,13 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F42" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F42" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="G42" s="3" t="n">
@@ -4007,7 +3995,7 @@
       <c r="J42" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -4025,10 +4013,10 @@
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -4038,10 +4026,10 @@
       <c r="U42" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4069,13 +4057,13 @@
       <c r="C43" s="3" t="n">
         <v>604.4</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4090,7 +4078,7 @@
       <c r="J43" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
@@ -4108,25 +4096,25 @@
       <c r="P43" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.8</v>
+        <v>32.2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V43" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V43" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4154,26 +4142,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4191,15 +4179,15 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>3119.5</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>131.1</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="9" t="n">
         <v>53.6</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4214,20 +4202,20 @@
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="9" t="n">
         <v>56.4</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="9" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>60.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
@@ -4235,7 +4223,7 @@
       <c r="Q45" s="9" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4247,10 +4235,10 @@
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="8" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4260,7 +4248,7 @@
         <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.7</v>
+        <v>50.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4278,13 +4266,13 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4299,13 +4287,13 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>11111111</v>
-      </c>
-      <c r="L46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4315,27 +4303,27 @@
         <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="9" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -47,14 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,10 +146,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -792,7 +792,7 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="8" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="8" t="n">
@@ -877,7 +877,7 @@
       <c r="K5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="M5" s="8" t="n">
@@ -962,7 +962,7 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="M6" s="8" t="n">
@@ -982,7 +982,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>67.5</v>
@@ -1045,8 +1045,8 @@
       <c r="K7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>13.4</v>
+      <c r="L7" s="8" t="n">
+        <v>15.4</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>15.2</v>
@@ -1073,7 +1073,7 @@
         <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>18.8</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
+        <v>37.7</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>24.4</v>
@@ -1130,14 +1130,14 @@
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>171.9</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>99</v>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
+        <v>182.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>126.5</v>
@@ -1215,7 +1215,7 @@
       <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="8" t="n">
@@ -1240,7 +1240,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2.8</v>
+        <v>89.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1298,9 +1298,9 @@
         <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>15</v>
       </c>
       <c r="M10" s="8" t="n">
@@ -1310,7 +1310,7 @@
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>28.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
@@ -1340,7 +1340,7 @@
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>86.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1386,10 +1386,10 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>13.7</v>
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>15.6</v>
@@ -1422,7 +1422,7 @@
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.4</v>
+        <v>20.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>95</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>51.1</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>25.7</v>
@@ -1473,17 +1473,17 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="8" t="n">
         <v>24.3</v>
@@ -1495,7 +1495,7 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>22.2</v>
+        <v>30.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1541,7 +1541,7 @@
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1558,7 +1558,7 @@
       <c r="L13" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1568,7 +1568,7 @@
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>23.8</v>
@@ -1595,7 +1595,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1643,7 +1643,7 @@
       <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1677,7 +1677,7 @@
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>20.3</v>
+        <v>22.3</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
@@ -1711,13 +1711,13 @@
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>12.6</v>
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1728,7 +1728,7 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>230.6</v>
+        <v>230</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>127.2</v>
@@ -1813,7 +1813,7 @@
       <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="9" t="n">
         <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1845,10 +1845,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.3</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1869,8 +1869,8 @@
       <c r="C17" s="3" t="n">
         <v>461.4</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>25.9</v>
+      <c r="D17" s="8" t="n">
+        <v>25.4</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13</v>
@@ -1891,12 +1891,12 @@
         <v>2.7</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1985,10 +1985,10 @@
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2135.6</v>
+        <v>335.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
@@ -2067,7 +2067,7 @@
         <v>14.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>19.8</v>
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.5</v>
@@ -2088,7 +2088,7 @@
         <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>36.1</v>
+        <v>56.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
@@ -2155,7 +2155,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2176,7 +2176,7 @@
         <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V20" s="8" t="n">
         <v>19.2</v>
@@ -2240,7 +2240,7 @@
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
@@ -2270,7 +2270,7 @@
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>98</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.8</v>
@@ -2325,7 +2325,7 @@
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.4</v>
+        <v>18.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2493,7 +2493,7 @@
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.2</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2545,9 +2545,9 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="E25" s="8" t="n">
@@ -2568,7 +2568,7 @@
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2578,7 +2578,7 @@
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2602,7 +2602,7 @@
         <v>2.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2632,7 +2632,7 @@
       <c r="C26" s="3" t="n">
         <v>268.3</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -2642,7 +2642,7 @@
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>71.2</v>
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2653,7 +2653,7 @@
       <c r="J26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K26" s="8" t="n">
+      <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="3" t="n">
@@ -2663,7 +2663,7 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>12.2</v>
+        <v>17.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2713,7 +2713,7 @@
       <c r="C27" s="3" t="n">
         <v>435.6</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="E27" s="8" t="n">
@@ -2734,7 +2734,7 @@
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="8" t="n">
+      <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="L27" s="3" t="n">
@@ -2774,7 +2774,7 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2798,7 +2798,7 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -2819,7 +2819,7 @@
       <c r="J28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2865,7 +2865,7 @@
         <v>98</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       <c r="C29" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="E29" s="8" t="n">
@@ -2904,11 +2904,11 @@
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K29" s="8" t="n">
-        <v>6.6</v>
+      <c r="K29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.1</v>
+        <v>13.9</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>15</v>
@@ -2968,8 +2968,8 @@
       <c r="C30" s="3" t="n">
         <v>156.9</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>1168.2</v>
+      <c r="D30" s="8" t="n">
+        <v>116.8</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>71.90000000000001</v>
@@ -2989,7 +2989,7 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K30" s="9" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
@@ -3012,7 +3012,7 @@
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -3051,8 +3051,8 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>123.4</v>
+      <c r="D31" s="8" t="n">
+        <v>23.4</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>14.4</v>
@@ -3061,7 +3061,7 @@
         <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3080,13 +3080,13 @@
         <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.8</v>
+        <v>0.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" s="8" t="n">
         <v>19.9</v>
@@ -3098,13 +3098,13 @@
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
@@ -3134,14 +3134,14 @@
       <c r="C32" s="3" t="n">
         <v>364.6</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>25.7</v>
+      <c r="D32" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>181.5</v>
+      <c r="F32" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
@@ -3153,27 +3153,27 @@
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
         <v>15</v>
       </c>
       <c r="R32" s="8" t="n">
@@ -3191,13 +3191,13 @@
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3215,13 +3215,13 @@
       <c r="C33" s="3" t="n">
         <v>411.2</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3254,7 +3254,7 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="R33" s="8" t="n">
@@ -3282,7 +3282,7 @@
         <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3298,15 +3298,15 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="D34" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3327,19 +3327,19 @@
       <c r="L34" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="M34" s="10" t="n">
-        <v>115</v>
+      <c r="M34" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>29.1</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="R34" s="8" t="n">
@@ -3349,7 +3349,7 @@
         <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2</v>
@@ -3367,7 +3367,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3385,13 +3385,13 @@
       <c r="C35" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3424,14 +3424,14 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R35" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>212.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3470,13 +3470,13 @@
       <c r="C36" s="3" t="n">
         <v>613.2</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3509,8 +3509,8 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>24</v>
+      <c r="Q36" s="3" t="n">
+        <v>27</v>
       </c>
       <c r="R36" s="8" t="n">
         <v>17.6</v>
@@ -3519,7 +3519,7 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>54.1</v>
+        <v>58.1</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.4</v>
@@ -3553,19 +3553,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>207.8</v>
-      </c>
-      <c r="D37" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>118.4</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.3</v>
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3592,9 +3592,9 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q37" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="8" t="n">
@@ -3604,7 +3604,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3809.1</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
@@ -3638,13 +3638,13 @@
       <c r="C38" s="3" t="n">
         <v>415.6</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3675,9 +3675,9 @@
         <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="R38" s="8" t="n">
@@ -3750,26 +3750,26 @@
       <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="12" t="n">
         <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3854,10 +3854,10 @@
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
@@ -3875,7 +3875,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       <c r="D41" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="8" t="n">
@@ -3923,7 +3923,7 @@
         <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3956,7 +3956,7 @@
         <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>12.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>97</v>
@@ -4106,10 +4106,10 @@
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>32.2</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>18.9</v>
+        <v>14.9</v>
       </c>
       <c r="V43" s="8" t="n">
         <v>21.4</v>
@@ -4121,7 +4121,7 @@
         <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>29.8</v>
+        <v>19.8</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>13</v>
@@ -4140,18 +4140,18 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
@@ -4209,18 +4209,18 @@
         <v>56.4</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>55.9</v>
+        <v>55.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>26</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" s="8" t="n">
         <v>126.3</v>
       </c>
       <c r="R45" s="8" t="n">
@@ -4242,7 +4242,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>302.8</v>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>223.9</v>
+        <v>623.9</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>26.2</v>
@@ -4288,13 +4288,13 @@
         <v>5.5</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
@@ -4315,13 +4315,13 @@
         <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
+        <v>50.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>218.4</v>
+      <c r="V46" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="W46" s="8" t="n">
         <v>16.6</v>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1214,7 +1214,7 @@
       <c r="J9" s="3" t="n">
         <v>1128.9</v>
       </c>
-      <c r="K9" s="3" t="n"/>
+      <c r="K9" s="13" t="n"/>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
@@ -1351,8 +1351,8 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="9" t="n">
         <v>1.6</v>
       </c>
@@ -1368,7 +1368,7 @@
       <c r="J11" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="14" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n">
         <v>14.9</v>
@@ -1427,7 +1427,7 @@
       <c r="D12" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="E12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="J12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K12" s="3" t="n"/>
+      <c r="K12" s="14" t="n"/>
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
@@ -1765,7 +1765,7 @@
       <c r="J16" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -1929,7 +1929,7 @@
       <c r="J18" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="11" t="n">
         <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -2004,7 +2004,7 @@
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -2081,7 +2081,7 @@
       <c r="J20" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2162,7 +2162,7 @@
       <c r="J21" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
@@ -2245,7 +2245,7 @@
       <c r="J22" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="L22" s="3" t="n">
@@ -2328,7 +2328,7 @@
       <c r="J23" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2865,7 +2865,7 @@
       <c r="C30" s="3" t="n">
         <v>1116.8</v>
       </c>
-      <c r="D30" s="14" t="n"/>
+      <c r="D30" s="13" t="n"/>
       <c r="E30" s="10" t="n">
         <v>14</v>
       </c>
@@ -2884,7 +2884,7 @@
       <c r="J30" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="13" t="n"/>
       <c r="L30" s="3" t="n">
         <v>13.7</v>
       </c>
@@ -3049,7 +3049,7 @@
       <c r="J32" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="14" t="n"/>
       <c r="L32" s="3" t="n">
         <v>15</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -3515,7 +3515,7 @@
       <c r="D38" s="10" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
+      <c r="E38" s="13" t="n"/>
       <c r="F38" s="10" t="n">
         <v>92.2</v>
       </c>
@@ -3845,7 +3845,7 @@
       <c r="D42" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="E42" s="13" t="n"/>
+      <c r="E42" s="14" t="n"/>
       <c r="F42" s="3" t="n">
         <v>18.7</v>
       </c>
@@ -4122,7 +4122,7 @@
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
